--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>25722.367</v>
+        <v>25729.878</v>
       </c>
       <c r="D2">
-        <v>21679.977</v>
+        <v>21688.557</v>
       </c>
       <c r="E2">
-        <v>29759.904</v>
+        <v>29775.451</v>
       </c>
       <c r="F2">
-        <v>178076.394</v>
+        <v>178042.393</v>
       </c>
       <c r="G2">
-        <v>160024.738</v>
+        <v>160006.216</v>
       </c>
       <c r="H2">
-        <v>196119.868</v>
+        <v>196137.69</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>23684047949.24</v>
+        <v>23680706748.437</v>
       </c>
       <c r="M2">
-        <v>21269503028.169</v>
+        <v>21271161493.346</v>
       </c>
       <c r="N2">
-        <v>26087734914.513</v>
+        <v>26083491100.128</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>15108.437</v>
+        <v>15110.214</v>
       </c>
       <c r="D3">
-        <v>12953.856</v>
+        <v>12951.233</v>
       </c>
       <c r="E3">
-        <v>17259.131</v>
+        <v>17257.975</v>
       </c>
       <c r="F3">
-        <v>117338.205</v>
+        <v>117338.817</v>
       </c>
       <c r="G3">
-        <v>104848.604</v>
+        <v>104836.87</v>
       </c>
       <c r="H3">
-        <v>129832.333</v>
+        <v>129826.284</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>15603183699.439</v>
+        <v>15603010888.765</v>
       </c>
       <c r="M3">
-        <v>13937901047.968</v>
+        <v>13939132720.094</v>
       </c>
       <c r="N3">
-        <v>17279320635.483</v>
+        <v>17279611387.549</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>51021.992</v>
+        <v>51018.737</v>
       </c>
       <c r="D4">
-        <v>45739.68</v>
+        <v>45734.834</v>
       </c>
       <c r="E4">
-        <v>56279.004</v>
+        <v>56280.911</v>
       </c>
       <c r="F4">
-        <v>449804.724</v>
+        <v>449673.81</v>
       </c>
       <c r="G4">
-        <v>421056.056</v>
+        <v>421004.135</v>
       </c>
       <c r="H4">
-        <v>478485.029</v>
+        <v>478401.67</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>59833757739.326</v>
+        <v>59821864707.115</v>
       </c>
       <c r="M4">
-        <v>56000157406.399</v>
+        <v>55992840336.365</v>
       </c>
       <c r="N4">
-        <v>63688689582.243</v>
+        <v>63678435405.602</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>13395.247</v>
+        <v>13406.403</v>
       </c>
       <c r="D5">
-        <v>11714.997</v>
+        <v>11724.991</v>
       </c>
       <c r="E5">
-        <v>15093.699</v>
+        <v>15108.132</v>
       </c>
       <c r="F5">
-        <v>8778.036</v>
+        <v>8782.048000000001</v>
       </c>
       <c r="G5">
-        <v>7786.956</v>
+        <v>7789.142</v>
       </c>
       <c r="H5">
-        <v>9777.217000000001</v>
+        <v>9785.058000000001</v>
       </c>
       <c r="I5">
-        <v>746217500.6210001</v>
+        <v>746963621.551</v>
       </c>
       <c r="J5">
-        <v>652323944.7180001</v>
+        <v>652787268.068</v>
       </c>
       <c r="K5">
-        <v>840626396.001</v>
+        <v>841509346.679</v>
       </c>
       <c r="L5">
-        <v>1167457991.966</v>
+        <v>1168086663.498</v>
       </c>
       <c r="M5">
-        <v>1035592184.785</v>
+        <v>1036161641.817</v>
       </c>
       <c r="N5">
-        <v>1300616179.505</v>
+        <v>1301832140.907</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>7571.039</v>
+        <v>7575.305</v>
       </c>
       <c r="D6">
-        <v>6649.074</v>
+        <v>6651.88</v>
       </c>
       <c r="E6">
-        <v>8505.76</v>
+        <v>8508.882</v>
       </c>
       <c r="F6">
-        <v>5278.483</v>
+        <v>5281.18</v>
       </c>
       <c r="G6">
-        <v>4644.359</v>
+        <v>4646.122</v>
       </c>
       <c r="H6">
-        <v>5917.104</v>
+        <v>5920.758</v>
       </c>
       <c r="I6">
-        <v>421910088.737</v>
+        <v>422153424.56</v>
       </c>
       <c r="J6">
-        <v>370304053.917</v>
+        <v>370440195.696</v>
       </c>
       <c r="K6">
-        <v>473852985.591</v>
+        <v>474172843.303</v>
       </c>
       <c r="L6">
-        <v>702250590.603</v>
+        <v>702640808.6900001</v>
       </c>
       <c r="M6">
-        <v>618116014.062</v>
+        <v>618381247.488</v>
       </c>
       <c r="N6">
-        <v>787243004.965</v>
+        <v>787492940.199</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>31960.146</v>
+        <v>31981.155</v>
       </c>
       <c r="D7">
-        <v>29312.945</v>
+        <v>29326.033</v>
       </c>
       <c r="E7">
-        <v>34624.212</v>
+        <v>34654.341</v>
       </c>
       <c r="F7">
-        <v>23989.288</v>
+        <v>24009.265</v>
       </c>
       <c r="G7">
-        <v>22245.551</v>
+        <v>22262.013</v>
       </c>
       <c r="H7">
-        <v>25743.521</v>
+        <v>25769.949</v>
       </c>
       <c r="I7">
-        <v>1780753009.305</v>
+        <v>1781926605.943</v>
       </c>
       <c r="J7">
-        <v>1632133847.291</v>
+        <v>1633476232.95</v>
       </c>
       <c r="K7">
-        <v>1929586300.951</v>
+        <v>1931141344.512</v>
       </c>
       <c r="L7">
-        <v>3190793864.358</v>
+        <v>3193509708.561</v>
       </c>
       <c r="M7">
-        <v>2959333719.751</v>
+        <v>2961416754.616</v>
       </c>
       <c r="N7">
-        <v>3423275640.094</v>
+        <v>3426744664.437</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>5867.114</v>
+        <v>5868.178</v>
       </c>
       <c r="D8">
-        <v>5279.85</v>
+        <v>5280.498</v>
       </c>
       <c r="E8">
-        <v>6461.851</v>
+        <v>6463.305</v>
       </c>
       <c r="F8">
-        <v>6173.739</v>
+        <v>6189.243</v>
       </c>
       <c r="G8">
-        <v>5486.748</v>
+        <v>5499.384</v>
       </c>
       <c r="H8">
-        <v>6875.431</v>
+        <v>6894.832</v>
       </c>
       <c r="I8">
-        <v>86848624.764</v>
+        <v>86871020.33499999</v>
       </c>
       <c r="J8">
-        <v>78196626.083</v>
+        <v>78196417.145</v>
       </c>
       <c r="K8">
-        <v>95639848.381</v>
+        <v>95650138.258</v>
       </c>
       <c r="L8">
-        <v>821018187.5089999</v>
+        <v>822981866.441</v>
       </c>
       <c r="M8">
-        <v>729793342.47</v>
+        <v>730944186.006</v>
       </c>
       <c r="N8">
-        <v>914707534.303</v>
+        <v>917547997.776</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3308.839</v>
+        <v>3310.489</v>
       </c>
       <c r="D9">
-        <v>2965.464</v>
+        <v>2968.918</v>
       </c>
       <c r="E9">
-        <v>3656.634</v>
+        <v>3657.727</v>
       </c>
       <c r="F9">
-        <v>3735.849</v>
+        <v>3741.553</v>
       </c>
       <c r="G9">
-        <v>3283.704</v>
+        <v>3290.395</v>
       </c>
       <c r="H9">
-        <v>4199.22</v>
+        <v>4205.796</v>
       </c>
       <c r="I9">
-        <v>48973238.386</v>
+        <v>49012826.735</v>
       </c>
       <c r="J9">
-        <v>43934305.498</v>
+        <v>43983835.518</v>
       </c>
       <c r="K9">
-        <v>54168950.177</v>
+        <v>54178060.985</v>
       </c>
       <c r="L9">
-        <v>496833091.226</v>
+        <v>497598614.032</v>
       </c>
       <c r="M9">
-        <v>436697931.848</v>
+        <v>437281791.132</v>
       </c>
       <c r="N9">
-        <v>558681144.342</v>
+        <v>559650290.822</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>17483.093</v>
+        <v>17489.617</v>
       </c>
       <c r="D10">
-        <v>16367.779</v>
+        <v>16376.492</v>
       </c>
       <c r="E10">
-        <v>18616.578</v>
+        <v>18621.089</v>
       </c>
       <c r="F10">
-        <v>22963.678</v>
+        <v>23001.489</v>
       </c>
       <c r="G10">
-        <v>21268.027</v>
+        <v>21296.371</v>
       </c>
       <c r="H10">
-        <v>24671.817</v>
+        <v>24724.58</v>
       </c>
       <c r="I10">
-        <v>258878154.008</v>
+        <v>258972242.627</v>
       </c>
       <c r="J10">
-        <v>242477402.584</v>
+        <v>242492908.662</v>
       </c>
       <c r="K10">
-        <v>275669642.67</v>
+        <v>275737854.604</v>
       </c>
       <c r="L10">
-        <v>3053443115.962</v>
+        <v>3059110583.559</v>
       </c>
       <c r="M10">
-        <v>2829656650.436</v>
+        <v>2833275627.417</v>
       </c>
       <c r="N10">
-        <v>3280261608.934</v>
+        <v>3287133786.168</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1000.863</v>
+        <v>1002.454</v>
       </c>
       <c r="D11">
-        <v>892.877</v>
+        <v>894.463</v>
       </c>
       <c r="E11">
-        <v>1111.166</v>
+        <v>1112.767</v>
       </c>
       <c r="F11">
-        <v>1526.326</v>
+        <v>1526.374</v>
       </c>
       <c r="G11">
-        <v>1366.111</v>
+        <v>1366.382</v>
       </c>
       <c r="H11">
-        <v>1692.733</v>
+        <v>1692.782</v>
       </c>
       <c r="I11">
-        <v>75269221.295</v>
+        <v>75388461.79099999</v>
       </c>
       <c r="J11">
-        <v>67137144.49699999</v>
+        <v>67287234.601</v>
       </c>
       <c r="K11">
-        <v>83567294.87199999</v>
+        <v>83702555.88500001</v>
       </c>
       <c r="L11">
-        <v>203010016.419</v>
+        <v>203010622.579</v>
       </c>
       <c r="M11">
-        <v>181540554.137</v>
+        <v>181674893.211</v>
       </c>
       <c r="N11">
-        <v>225113392.357</v>
+        <v>225062239.451</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>587.981</v>
+        <v>588.393</v>
       </c>
       <c r="D12">
-        <v>515.426</v>
+        <v>515.668</v>
       </c>
       <c r="E12">
-        <v>662.628</v>
+        <v>663.357</v>
       </c>
       <c r="F12">
-        <v>972.885</v>
+        <v>973.622</v>
       </c>
       <c r="G12">
-        <v>852.321</v>
+        <v>852.765</v>
       </c>
       <c r="H12">
-        <v>1096.623</v>
+        <v>1098.387</v>
       </c>
       <c r="I12">
-        <v>44210178.884</v>
+        <v>44255543.584</v>
       </c>
       <c r="J12">
-        <v>38780864.539</v>
+        <v>38813461.754</v>
       </c>
       <c r="K12">
-        <v>49875364.464</v>
+        <v>49911754.276</v>
       </c>
       <c r="L12">
-        <v>129392655.816</v>
+        <v>129468697.772</v>
       </c>
       <c r="M12">
-        <v>113392171.664</v>
+        <v>113401929.341</v>
       </c>
       <c r="N12">
-        <v>145902076.836</v>
+        <v>146030884.165</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>3180.426</v>
+        <v>3183.055</v>
       </c>
       <c r="D13">
-        <v>2955.894</v>
+        <v>2958.096</v>
       </c>
       <c r="E13">
-        <v>3407.302</v>
+        <v>3409.737</v>
       </c>
       <c r="F13">
-        <v>5753.516</v>
+        <v>5750.614</v>
       </c>
       <c r="G13">
-        <v>5346.211</v>
+        <v>5343.314</v>
       </c>
       <c r="H13">
-        <v>6168.679</v>
+        <v>6167.268</v>
       </c>
       <c r="I13">
-        <v>239166302.122</v>
+        <v>239380760.64</v>
       </c>
       <c r="J13">
-        <v>222274992.42</v>
+        <v>222509423.34</v>
       </c>
       <c r="K13">
-        <v>256338931.917</v>
+        <v>256465963.093</v>
       </c>
       <c r="L13">
-        <v>765193890.454</v>
+        <v>764758932.854</v>
       </c>
       <c r="M13">
-        <v>711036514.972</v>
+        <v>710467826.3329999</v>
       </c>
       <c r="N13">
-        <v>820464019.603</v>
+        <v>819892212.604</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>5672.175</v>
+        <v>5673.166</v>
       </c>
       <c r="D14">
-        <v>4750.701</v>
+        <v>4750.27</v>
       </c>
       <c r="E14">
-        <v>6599.459</v>
+        <v>6599.608</v>
       </c>
       <c r="F14">
-        <v>7075.131</v>
+        <v>7077.777</v>
       </c>
       <c r="G14">
-        <v>6068.608</v>
+        <v>6074.216</v>
       </c>
       <c r="H14">
-        <v>8090.055</v>
+        <v>8092.616</v>
       </c>
       <c r="I14">
-        <v>95534587.727</v>
+        <v>95539330.32700001</v>
       </c>
       <c r="J14">
-        <v>80047703.661</v>
+        <v>80085031.398</v>
       </c>
       <c r="K14">
-        <v>111081600.637</v>
+        <v>111123455.073</v>
       </c>
       <c r="L14">
-        <v>940843072.039</v>
+        <v>941132810.011</v>
       </c>
       <c r="M14">
-        <v>806846566.397</v>
+        <v>807024974.622</v>
       </c>
       <c r="N14">
-        <v>1075966067.976</v>
+        <v>1075963912.15</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>3196.344</v>
+        <v>3194.468</v>
       </c>
       <c r="D15">
-        <v>2677.887</v>
+        <v>2676.588</v>
       </c>
       <c r="E15">
-        <v>3721.284</v>
+        <v>3718.148</v>
       </c>
       <c r="F15">
-        <v>4013.396</v>
+        <v>4019.094</v>
       </c>
       <c r="G15">
-        <v>3448.675</v>
+        <v>3453.226</v>
       </c>
       <c r="H15">
-        <v>4582.449</v>
+        <v>4589.748</v>
       </c>
       <c r="I15">
-        <v>53793868.634</v>
+        <v>53766187.279</v>
       </c>
       <c r="J15">
-        <v>45034705.45</v>
+        <v>45029607.171</v>
       </c>
       <c r="K15">
-        <v>62609174.322</v>
+        <v>62572471.428</v>
       </c>
       <c r="L15">
-        <v>533618570.776</v>
+        <v>534420088.935</v>
       </c>
       <c r="M15">
-        <v>458693341.162</v>
+        <v>459573208.29</v>
       </c>
       <c r="N15">
-        <v>609980595.853</v>
+        <v>610663362.113</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>13048.349</v>
+        <v>13043.467</v>
       </c>
       <c r="D16">
-        <v>11635.839</v>
+        <v>11629.726</v>
       </c>
       <c r="E16">
-        <v>14471.07</v>
+        <v>14461.99</v>
       </c>
       <c r="F16">
-        <v>18624.454</v>
+        <v>18627.641</v>
       </c>
       <c r="G16">
-        <v>16883.203</v>
+        <v>16885.812</v>
       </c>
       <c r="H16">
-        <v>20385.639</v>
+        <v>20386.336</v>
       </c>
       <c r="I16">
-        <v>219754216.938</v>
+        <v>219678837.327</v>
       </c>
       <c r="J16">
-        <v>195878424.831</v>
+        <v>195815831.285</v>
       </c>
       <c r="K16">
-        <v>243793417.036</v>
+        <v>243660454.965</v>
       </c>
       <c r="L16">
-        <v>2477669963.923</v>
+        <v>2477793173.835</v>
       </c>
       <c r="M16">
-        <v>2245266225.715</v>
+        <v>2246419135.736</v>
       </c>
       <c r="N16">
-        <v>2711251201.514</v>
+        <v>2711399915.735</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>24980.37</v>
+        <v>20914.908</v>
       </c>
       <c r="D17">
-        <v>22746.509</v>
+        <v>19022.028</v>
       </c>
       <c r="E17">
-        <v>27222.389</v>
+        <v>22824.753</v>
       </c>
       <c r="F17">
-        <v>50679.782</v>
+        <v>4768.862</v>
       </c>
       <c r="G17">
-        <v>44651.618</v>
+        <v>4211.961</v>
       </c>
       <c r="H17">
-        <v>56771.793</v>
+        <v>5336.977</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>6741658865.266</v>
+        <v>634348137.465</v>
       </c>
       <c r="M17">
-        <v>5937381049.618</v>
+        <v>560126302.415</v>
       </c>
       <c r="N17">
-        <v>7547457489.12</v>
+        <v>709203654.511</v>
       </c>
     </row>
     <row r="18">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>14702.732</v>
+        <v>12295.081</v>
       </c>
       <c r="D18">
-        <v>13317.221</v>
+        <v>11123.402</v>
       </c>
       <c r="E18">
-        <v>16075.806</v>
+        <v>13463.932</v>
       </c>
       <c r="F18">
-        <v>32305.784</v>
+        <v>3028.799</v>
       </c>
       <c r="G18">
-        <v>28322.921</v>
+        <v>2658.878</v>
       </c>
       <c r="H18">
-        <v>36305.399</v>
+        <v>3402.872</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>4297972829.281</v>
+        <v>402972119.67</v>
       </c>
       <c r="M18">
-        <v>3768824832.544</v>
+        <v>353728501.719</v>
       </c>
       <c r="N18">
-        <v>4830173199.923</v>
+        <v>452520691.123</v>
       </c>
     </row>
     <row r="19">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>84529.088</v>
+        <v>70343.86199999999</v>
       </c>
       <c r="D19">
-        <v>79863.83100000001</v>
+        <v>66406.77</v>
       </c>
       <c r="E19">
-        <v>89182.386</v>
+        <v>74272.74400000001</v>
       </c>
       <c r="F19">
-        <v>222461.96</v>
+        <v>20546.65</v>
       </c>
       <c r="G19">
-        <v>205930.49</v>
+        <v>19031.543</v>
       </c>
       <c r="H19">
-        <v>239015.994</v>
+        <v>22077.397</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,13 +1281,13 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>29588690109.058</v>
+        <v>2733133420.948</v>
       </c>
       <c r="M19">
-        <v>27407629754.588</v>
+        <v>2533645602.175</v>
       </c>
       <c r="N19">
-        <v>31798860521.552</v>
+        <v>2935046811.452</v>
       </c>
     </row>
     <row r="20">
@@ -1297,40 +1297,40 @@
         </is>
       </c>
       <c r="C20">
-        <v>230483.806</v>
+        <v>209870.001</v>
       </c>
       <c r="D20">
-        <v>211646.294</v>
+        <v>192305.823</v>
       </c>
       <c r="E20">
-        <v>249412.224</v>
+        <v>227540.512</v>
       </c>
       <c r="F20">
-        <v>414332.307</v>
+        <v>137324.211</v>
       </c>
       <c r="G20">
-        <v>377585.503</v>
+        <v>124661.524</v>
       </c>
       <c r="H20">
-        <v>451293.674</v>
+        <v>150145.356</v>
       </c>
       <c r="I20">
-        <v>4071308991.421</v>
+        <v>4073908862.699</v>
       </c>
       <c r="J20">
-        <v>3668524015.489</v>
+        <v>3670917447.588</v>
       </c>
       <c r="K20">
-        <v>4476809907.019001</v>
+        <v>4479826243.061</v>
       </c>
       <c r="L20">
-        <v>55109846814.656</v>
+        <v>18264966248.85</v>
       </c>
       <c r="M20">
-        <v>50239800854.149</v>
+        <v>16583523622.318</v>
       </c>
       <c r="N20">
-        <v>60029953676.877</v>
+        <v>19966185503.613</v>
       </c>
     </row>
     <row r="21">
@@ -1340,40 +1340,40 @@
         </is>
       </c>
       <c r="C21">
-        <v>322336.602</v>
+        <v>301728.83</v>
       </c>
       <c r="D21">
-        <v>292019.807</v>
+        <v>272680.447</v>
       </c>
       <c r="E21">
-        <v>352710.263</v>
+        <v>330854.8489999999</v>
       </c>
       <c r="F21">
-        <v>1159551.63</v>
+        <v>882379.2309999998</v>
       </c>
       <c r="G21">
-        <v>1063514.901</v>
+        <v>810508.7450000001</v>
       </c>
       <c r="H21">
-        <v>1255730.904</v>
+        <v>954511</v>
       </c>
       <c r="I21">
-        <v>4071308991.421</v>
+        <v>4073908862.699</v>
       </c>
       <c r="J21">
-        <v>3668524015.489</v>
+        <v>3670917447.588</v>
       </c>
       <c r="K21">
-        <v>4476809907.019001</v>
+        <v>4479826243.061</v>
       </c>
       <c r="L21">
-        <v>154230836202.661</v>
+        <v>117370548593.167</v>
       </c>
       <c r="M21">
-        <v>141447362336.685</v>
+        <v>107786658172.123</v>
       </c>
       <c r="N21">
-        <v>167085698809.116</v>
+        <v>127007723396.892</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -438,22 +438,22 @@
         </is>
       </c>
       <c r="C2">
-        <v>25729.878</v>
+        <v>34049.409</v>
       </c>
       <c r="D2">
-        <v>21688.557</v>
+        <v>31641.343</v>
       </c>
       <c r="E2">
-        <v>29775.451</v>
+        <v>36462.905</v>
       </c>
       <c r="F2">
-        <v>178042.393</v>
+        <v>308698.565</v>
       </c>
       <c r="G2">
-        <v>160006.216</v>
+        <v>295683.071</v>
       </c>
       <c r="H2">
-        <v>196137.69</v>
+        <v>321730.497</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,13 +465,13 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>23680706748.437</v>
+        <v>41056520139.482</v>
       </c>
       <c r="M2">
-        <v>21271161493.346</v>
+        <v>39324435939.413</v>
       </c>
       <c r="N2">
-        <v>26083491100.128</v>
+        <v>42788150076.078</v>
       </c>
     </row>
     <row r="3">
@@ -486,22 +486,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>15110.214</v>
+        <v>30892.621</v>
       </c>
       <c r="D3">
-        <v>12951.233</v>
+        <v>28952.467</v>
       </c>
       <c r="E3">
-        <v>17257.975</v>
+        <v>32820.011</v>
       </c>
       <c r="F3">
-        <v>117338.817</v>
+        <v>291691.451</v>
       </c>
       <c r="G3">
-        <v>104836.87</v>
+        <v>281081.82</v>
       </c>
       <c r="H3">
-        <v>129826.284</v>
+        <v>302293.371</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,13 +513,13 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>15603010888.765</v>
+        <v>38793008567.954</v>
       </c>
       <c r="M3">
-        <v>13939132720.094</v>
+        <v>37378154366.943</v>
       </c>
       <c r="N3">
-        <v>17279611387.549</v>
+        <v>40217566983.298</v>
       </c>
     </row>
     <row r="4">
@@ -534,22 +534,22 @@
         </is>
       </c>
       <c r="C4">
-        <v>51018.737</v>
+        <v>34856.981</v>
       </c>
       <c r="D4">
-        <v>45734.834</v>
+        <v>32706.019</v>
       </c>
       <c r="E4">
-        <v>56280.911</v>
+        <v>36998.416</v>
       </c>
       <c r="F4">
-        <v>449673.81</v>
+        <v>374763.56</v>
       </c>
       <c r="G4">
-        <v>421004.135</v>
+        <v>361438.191</v>
       </c>
       <c r="H4">
-        <v>478401.67</v>
+        <v>388100.677</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>59821864707.115</v>
+        <v>49851959804.593</v>
       </c>
       <c r="M4">
-        <v>55992840336.365</v>
+        <v>48065294642.788</v>
       </c>
       <c r="N4">
-        <v>63678435405.602</v>
+        <v>51641150657.794</v>
       </c>
     </row>
     <row r="5">
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="C5">
-        <v>13406.403</v>
+        <v>19522.368</v>
       </c>
       <c r="D5">
-        <v>11724.991</v>
+        <v>18429.798</v>
       </c>
       <c r="E5">
-        <v>15108.132</v>
+        <v>20629.758</v>
       </c>
       <c r="F5">
-        <v>8782.048000000001</v>
+        <v>15535.261</v>
       </c>
       <c r="G5">
-        <v>7789.142</v>
+        <v>14755.984</v>
       </c>
       <c r="H5">
-        <v>9785.058000000001</v>
+        <v>16322.338</v>
       </c>
       <c r="I5">
-        <v>746963621.551</v>
+        <v>1087509723.915</v>
       </c>
       <c r="J5">
-        <v>652787268.068</v>
+        <v>1026502557.435</v>
       </c>
       <c r="K5">
-        <v>841509346.679</v>
+        <v>1148957113.77</v>
       </c>
       <c r="L5">
-        <v>1168086663.498</v>
+        <v>2066150897.081</v>
       </c>
       <c r="M5">
-        <v>1036161641.817</v>
+        <v>1962729276.563</v>
       </c>
       <c r="N5">
-        <v>1301832140.907</v>
+        <v>2170818141.95</v>
       </c>
     </row>
     <row r="6">
@@ -630,40 +630,40 @@
         </is>
       </c>
       <c r="C6">
-        <v>7575.305</v>
+        <v>15629.423</v>
       </c>
       <c r="D6">
-        <v>6651.88</v>
+        <v>14864.087</v>
       </c>
       <c r="E6">
-        <v>8508.882</v>
+        <v>16403.455</v>
       </c>
       <c r="F6">
-        <v>5281.18</v>
+        <v>12847.594</v>
       </c>
       <c r="G6">
-        <v>4646.122</v>
+        <v>12273.394</v>
       </c>
       <c r="H6">
-        <v>5920.758</v>
+        <v>13431.71</v>
       </c>
       <c r="I6">
-        <v>422153424.56</v>
+        <v>870706606.089</v>
       </c>
       <c r="J6">
-        <v>370440195.696</v>
+        <v>828088414.568</v>
       </c>
       <c r="K6">
-        <v>474172843.303</v>
+        <v>913804891.925</v>
       </c>
       <c r="L6">
-        <v>702640808.6900001</v>
+        <v>1708827181.884</v>
       </c>
       <c r="M6">
-        <v>618381247.488</v>
+        <v>1632379050.51</v>
       </c>
       <c r="N6">
-        <v>787492940.199</v>
+        <v>1786480557.537</v>
       </c>
     </row>
     <row r="7">
@@ -678,40 +678,40 @@
         </is>
       </c>
       <c r="C7">
-        <v>31981.155</v>
+        <v>19540.313</v>
       </c>
       <c r="D7">
-        <v>29326.033</v>
+        <v>18587.38</v>
       </c>
       <c r="E7">
-        <v>34654.341</v>
+        <v>20505.26</v>
       </c>
       <c r="F7">
-        <v>24009.265</v>
+        <v>17642.669</v>
       </c>
       <c r="G7">
-        <v>22262.013</v>
+        <v>16890.77</v>
       </c>
       <c r="H7">
-        <v>25769.949</v>
+        <v>18401.59</v>
       </c>
       <c r="I7">
-        <v>1781926605.943</v>
+        <v>1088430310.521</v>
       </c>
       <c r="J7">
-        <v>1633476232.95</v>
+        <v>1035056644.269</v>
       </c>
       <c r="K7">
-        <v>1931141344.512</v>
+        <v>1142498325.722</v>
       </c>
       <c r="L7">
-        <v>3193509708.561</v>
+        <v>2346637565.489</v>
       </c>
       <c r="M7">
-        <v>2961416754.616</v>
+        <v>2246530620.074</v>
       </c>
       <c r="N7">
-        <v>3426744664.437</v>
+        <v>2447903960.216</v>
       </c>
     </row>
     <row r="8">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="C8">
-        <v>5868.178</v>
+        <v>10515.488</v>
       </c>
       <c r="D8">
-        <v>5280.498</v>
+        <v>10003.627</v>
       </c>
       <c r="E8">
-        <v>6463.305</v>
+        <v>11039.813</v>
       </c>
       <c r="F8">
-        <v>6189.243</v>
+        <v>13572.93</v>
       </c>
       <c r="G8">
-        <v>5499.384</v>
+        <v>12795.847</v>
       </c>
       <c r="H8">
-        <v>6894.832</v>
+        <v>14384.945</v>
       </c>
       <c r="I8">
-        <v>86871020.33499999</v>
+        <v>155674252.981</v>
       </c>
       <c r="J8">
-        <v>78196417.145</v>
+        <v>148116429.745</v>
       </c>
       <c r="K8">
-        <v>95650138.258</v>
+        <v>163421607.115</v>
       </c>
       <c r="L8">
-        <v>822981866.441</v>
+        <v>1805043633.704</v>
       </c>
       <c r="M8">
-        <v>730944186.006</v>
+        <v>1701699773.74</v>
       </c>
       <c r="N8">
-        <v>917547997.776</v>
+        <v>1912896347.35</v>
       </c>
     </row>
     <row r="9">
@@ -774,40 +774,40 @@
         </is>
       </c>
       <c r="C9">
-        <v>3310.489</v>
+        <v>7888.195</v>
       </c>
       <c r="D9">
-        <v>2968.918</v>
+        <v>7550.356</v>
       </c>
       <c r="E9">
-        <v>3657.727</v>
+        <v>8227.514999999999</v>
       </c>
       <c r="F9">
-        <v>3741.553</v>
+        <v>10158.23</v>
       </c>
       <c r="G9">
-        <v>3290.395</v>
+        <v>9657.742</v>
       </c>
       <c r="H9">
-        <v>4205.796</v>
+        <v>10670.856</v>
       </c>
       <c r="I9">
-        <v>49012826.735</v>
+        <v>116793443.135</v>
       </c>
       <c r="J9">
-        <v>43983835.518</v>
+        <v>111818763.883</v>
       </c>
       <c r="K9">
-        <v>54178060.985</v>
+        <v>121848043.361</v>
       </c>
       <c r="L9">
-        <v>497598614.032</v>
+        <v>1351001949.337</v>
       </c>
       <c r="M9">
-        <v>437281791.132</v>
+        <v>1284083548.561</v>
       </c>
       <c r="N9">
-        <v>559650290.822</v>
+        <v>1419347434.618</v>
       </c>
     </row>
     <row r="10">
@@ -822,40 +822,40 @@
         </is>
       </c>
       <c r="C10">
-        <v>17489.617</v>
+        <v>12202.606</v>
       </c>
       <c r="D10">
-        <v>16376.492</v>
+        <v>11702.076</v>
       </c>
       <c r="E10">
-        <v>18621.089</v>
+        <v>12710.426</v>
       </c>
       <c r="F10">
-        <v>23001.489</v>
+        <v>18668.542</v>
       </c>
       <c r="G10">
-        <v>21296.371</v>
+        <v>17767.994</v>
       </c>
       <c r="H10">
-        <v>24724.58</v>
+        <v>19590.188</v>
       </c>
       <c r="I10">
-        <v>258972242.627</v>
+        <v>180683209.155</v>
       </c>
       <c r="J10">
-        <v>242492908.662</v>
+        <v>173307352.39</v>
       </c>
       <c r="K10">
-        <v>275737854.604</v>
+        <v>188221866.05</v>
       </c>
       <c r="L10">
-        <v>3059110583.559</v>
+        <v>2482826348.173</v>
       </c>
       <c r="M10">
-        <v>2833275627.417</v>
+        <v>2363795781.389</v>
       </c>
       <c r="N10">
-        <v>3287133786.168</v>
+        <v>2605166073.858</v>
       </c>
     </row>
     <row r="11">
@@ -870,40 +870,40 @@
         </is>
       </c>
       <c r="C11">
-        <v>1002.454</v>
+        <v>2061.315</v>
       </c>
       <c r="D11">
-        <v>894.463</v>
+        <v>1947.545</v>
       </c>
       <c r="E11">
-        <v>1112.767</v>
+        <v>2179.217</v>
       </c>
       <c r="F11">
-        <v>1526.374</v>
+        <v>3637.914</v>
       </c>
       <c r="G11">
-        <v>1366.382</v>
+        <v>3432.431</v>
       </c>
       <c r="H11">
-        <v>1692.782</v>
+        <v>3851.968</v>
       </c>
       <c r="I11">
-        <v>75388461.79099999</v>
+        <v>155028017.311</v>
       </c>
       <c r="J11">
-        <v>67287234.601</v>
+        <v>146404317.481</v>
       </c>
       <c r="K11">
-        <v>83702555.88500001</v>
+        <v>163824978.991</v>
       </c>
       <c r="L11">
-        <v>203010622.579</v>
+        <v>483855512.778</v>
       </c>
       <c r="M11">
-        <v>181674893.211</v>
+        <v>456413429.3</v>
       </c>
       <c r="N11">
-        <v>225062239.451</v>
+        <v>512324804.105</v>
       </c>
     </row>
     <row r="12">
@@ -918,40 +918,40 @@
         </is>
       </c>
       <c r="C12">
-        <v>588.393</v>
+        <v>1589.586</v>
       </c>
       <c r="D12">
-        <v>515.668</v>
+        <v>1509.83</v>
       </c>
       <c r="E12">
-        <v>663.357</v>
+        <v>1670.534</v>
       </c>
       <c r="F12">
-        <v>973.622</v>
+        <v>2817.139</v>
       </c>
       <c r="G12">
-        <v>852.765</v>
+        <v>2673.513</v>
       </c>
       <c r="H12">
-        <v>1098.387</v>
+        <v>2963.291</v>
       </c>
       <c r="I12">
-        <v>44255543.584</v>
+        <v>119551979.618</v>
       </c>
       <c r="J12">
-        <v>38813461.754</v>
+        <v>113582967.64</v>
       </c>
       <c r="K12">
-        <v>49911754.276</v>
+        <v>125621285.018</v>
       </c>
       <c r="L12">
-        <v>129468697.772</v>
+        <v>374643304.057</v>
       </c>
       <c r="M12">
-        <v>113401929.341</v>
+        <v>355596299.421</v>
       </c>
       <c r="N12">
-        <v>146030884.165</v>
+        <v>394125231.016</v>
       </c>
     </row>
     <row r="13">
@@ -966,40 +966,40 @@
         </is>
       </c>
       <c r="C13">
-        <v>3183.055</v>
+        <v>2502.239</v>
       </c>
       <c r="D13">
-        <v>2958.096</v>
+        <v>2385.756</v>
       </c>
       <c r="E13">
-        <v>3409.737</v>
+        <v>2620.712</v>
       </c>
       <c r="F13">
-        <v>5750.614</v>
+        <v>5079.879</v>
       </c>
       <c r="G13">
-        <v>5343.314</v>
+        <v>4835.147</v>
       </c>
       <c r="H13">
-        <v>6167.268</v>
+        <v>5328.369</v>
       </c>
       <c r="I13">
-        <v>239380760.64</v>
+        <v>188172838.929</v>
       </c>
       <c r="J13">
-        <v>222509423.34</v>
+        <v>179419234.869</v>
       </c>
       <c r="K13">
-        <v>256465963.093</v>
+        <v>197076931.247</v>
       </c>
       <c r="L13">
-        <v>764758932.854</v>
+        <v>675557738.554</v>
       </c>
       <c r="M13">
-        <v>710467826.3329999</v>
+        <v>643040953.012</v>
       </c>
       <c r="N13">
-        <v>819892212.604</v>
+        <v>708641003.199</v>
       </c>
     </row>
     <row r="14">
@@ -1014,40 +1014,40 @@
         </is>
       </c>
       <c r="C14">
-        <v>5673.166</v>
+        <v>7213.704</v>
       </c>
       <c r="D14">
-        <v>4750.27</v>
+        <v>6674.728</v>
       </c>
       <c r="E14">
-        <v>6599.608</v>
+        <v>7755.744</v>
       </c>
       <c r="F14">
-        <v>7077.777</v>
+        <v>10776.984</v>
       </c>
       <c r="G14">
-        <v>6074.216</v>
+        <v>10110.024</v>
       </c>
       <c r="H14">
-        <v>8092.616</v>
+        <v>11452.362</v>
       </c>
       <c r="I14">
-        <v>95539330.32700001</v>
+        <v>121477420.73</v>
       </c>
       <c r="J14">
-        <v>80085031.398</v>
+        <v>112414274.203</v>
       </c>
       <c r="K14">
-        <v>111123455.073</v>
+        <v>130611981.111</v>
       </c>
       <c r="L14">
-        <v>941132810.011</v>
+        <v>1433187243.799</v>
       </c>
       <c r="M14">
-        <v>807024974.622</v>
+        <v>1344550931.643</v>
       </c>
       <c r="N14">
-        <v>1075963912.15</v>
+        <v>1522907246.314</v>
       </c>
     </row>
     <row r="15">
@@ -1062,40 +1062,40 @@
         </is>
       </c>
       <c r="C15">
-        <v>3194.468</v>
+        <v>5565.41</v>
       </c>
       <c r="D15">
-        <v>2676.588</v>
+        <v>5172.745</v>
       </c>
       <c r="E15">
-        <v>3718.148</v>
+        <v>5963.294</v>
       </c>
       <c r="F15">
-        <v>4019.094</v>
+        <v>8304.186</v>
       </c>
       <c r="G15">
-        <v>3453.226</v>
+        <v>7874.326</v>
       </c>
       <c r="H15">
-        <v>4589.748</v>
+        <v>8737.806</v>
       </c>
       <c r="I15">
-        <v>53766187.279</v>
+        <v>93710939.579</v>
       </c>
       <c r="J15">
-        <v>45029607.171</v>
+        <v>87085376.517</v>
       </c>
       <c r="K15">
-        <v>62572471.428</v>
+        <v>100379221.359</v>
       </c>
       <c r="L15">
-        <v>534420088.935</v>
+        <v>1104282255.817</v>
       </c>
       <c r="M15">
-        <v>459573208.29</v>
+        <v>1047514511.451</v>
       </c>
       <c r="N15">
-        <v>610663362.113</v>
+        <v>1162164992.642</v>
       </c>
     </row>
     <row r="16">
@@ -1110,40 +1110,40 @@
         </is>
       </c>
       <c r="C16">
-        <v>13043.467</v>
+        <v>6906.579</v>
       </c>
       <c r="D16">
-        <v>11629.726</v>
+        <v>6439.128</v>
       </c>
       <c r="E16">
-        <v>14461.99</v>
+        <v>7379.192</v>
       </c>
       <c r="F16">
-        <v>18627.641</v>
+        <v>11261.063</v>
       </c>
       <c r="G16">
-        <v>16885.812</v>
+        <v>10637.399</v>
       </c>
       <c r="H16">
-        <v>20386.336</v>
+        <v>11896.311</v>
       </c>
       <c r="I16">
-        <v>219678837.327</v>
+        <v>116314411.592</v>
       </c>
       <c r="J16">
-        <v>195815831.285</v>
+        <v>108394180.913</v>
       </c>
       <c r="K16">
-        <v>243660454.965</v>
+        <v>124312662.065</v>
       </c>
       <c r="L16">
-        <v>2477793173.835</v>
+        <v>1497944344.905</v>
       </c>
       <c r="M16">
-        <v>2246419135.736</v>
+        <v>1414513897.945</v>
       </c>
       <c r="N16">
-        <v>2711399915.735</v>
+        <v>1582087740.092</v>
       </c>
     </row>
     <row r="17">
@@ -1158,22 +1158,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>20914.908</v>
+        <v>40472.983</v>
       </c>
       <c r="D17">
-        <v>19022.028</v>
+        <v>38821.135</v>
       </c>
       <c r="E17">
-        <v>22824.753</v>
+        <v>42148.516</v>
       </c>
       <c r="F17">
-        <v>4768.862</v>
+        <v>11432.064</v>
       </c>
       <c r="G17">
-        <v>4211.961</v>
+        <v>10792.565</v>
       </c>
       <c r="H17">
-        <v>5336.977</v>
+        <v>12084.547</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>634348137.465</v>
+        <v>1520471945.813</v>
       </c>
       <c r="M17">
-        <v>560126302.415</v>
+        <v>1435656257.882</v>
       </c>
       <c r="N17">
-        <v>709203654.511</v>
+        <v>1607322757.135</v>
       </c>
     </row>
     <row r="18">
@@ -1206,22 +1206,22 @@
         </is>
       </c>
       <c r="C18">
-        <v>12295.081</v>
+        <v>30091.127</v>
       </c>
       <c r="D18">
-        <v>11123.402</v>
+        <v>29029.478</v>
       </c>
       <c r="E18">
-        <v>13463.932</v>
+        <v>31157.65</v>
       </c>
       <c r="F18">
-        <v>3028.799</v>
+        <v>8482.531000000001</v>
       </c>
       <c r="G18">
-        <v>2658.878</v>
+        <v>8086.008</v>
       </c>
       <c r="H18">
-        <v>3402.872</v>
+        <v>8886.552</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,13 +1233,13 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>402972119.67</v>
+        <v>1128339741.959</v>
       </c>
       <c r="M18">
-        <v>353728501.719</v>
+        <v>1075408459.946</v>
       </c>
       <c r="N18">
-        <v>452520691.123</v>
+        <v>1182139869.437</v>
       </c>
     </row>
     <row r="19">
@@ -1254,22 +1254,22 @@
         </is>
       </c>
       <c r="C19">
-        <v>70343.86199999999</v>
+        <v>53804.46</v>
       </c>
       <c r="D19">
-        <v>66406.77</v>
+        <v>51975.673</v>
       </c>
       <c r="E19">
-        <v>74272.74400000001</v>
+        <v>55645.687</v>
       </c>
       <c r="F19">
-        <v>20546.65</v>
+        <v>17973.893</v>
       </c>
       <c r="G19">
-        <v>19031.543</v>
+        <v>17143.719</v>
       </c>
       <c r="H19">
-        <v>22077.397</v>
+        <v>18816.164</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,99 +1281,541 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2733133420.948</v>
+        <v>2390829625.806</v>
       </c>
       <c r="M19">
-        <v>2533645602.175</v>
+        <v>2280890956.502</v>
       </c>
       <c r="N19">
-        <v>2935046811.452</v>
+        <v>2502589681.858</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All</t>
         </is>
       </c>
       <c r="C20">
-        <v>209870.001</v>
+        <v>30606.289</v>
       </c>
       <c r="D20">
-        <v>192305.823</v>
+        <v>29256.059</v>
       </c>
       <c r="E20">
-        <v>227540.512</v>
+        <v>31977.754</v>
       </c>
       <c r="F20">
-        <v>137324.211</v>
+        <v>42399.702</v>
       </c>
       <c r="G20">
-        <v>124661.524</v>
+        <v>40221.583</v>
       </c>
       <c r="H20">
-        <v>150145.356</v>
+        <v>44645.989</v>
       </c>
       <c r="I20">
-        <v>4073908862.699</v>
+        <v>453150905.271</v>
       </c>
       <c r="J20">
-        <v>3670917447.588</v>
+        <v>433242546.018</v>
       </c>
       <c r="K20">
-        <v>4479826243.061</v>
+        <v>473491516.526</v>
       </c>
       <c r="L20">
-        <v>18264966248.85</v>
+        <v>5638871931.214</v>
       </c>
       <c r="M20">
-        <v>16583523622.318</v>
+        <v>5349579103.690001</v>
       </c>
       <c r="N20">
-        <v>19966185503.613</v>
+        <v>5937409855.826</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>All</t>
         </is>
       </c>
       <c r="C21">
-        <v>301728.83</v>
+        <v>54692.10399999999</v>
       </c>
       <c r="D21">
-        <v>272680.447</v>
+        <v>51881.265</v>
       </c>
       <c r="E21">
-        <v>330854.8489999999</v>
+        <v>57538.473</v>
       </c>
       <c r="F21">
-        <v>882379.2309999998</v>
+        <v>46025.524</v>
       </c>
       <c r="G21">
-        <v>810508.7450000001</v>
+        <v>43920.148</v>
       </c>
       <c r="H21">
-        <v>954511</v>
+        <v>48155.638</v>
       </c>
       <c r="I21">
-        <v>4073908862.699</v>
+        <v>3046646640.525</v>
       </c>
       <c r="J21">
-        <v>3670917447.588</v>
+        <v>2889647616.272</v>
       </c>
       <c r="K21">
-        <v>4479826243.061</v>
+        <v>3205260331.417</v>
       </c>
       <c r="L21">
-        <v>117370548593.167</v>
+        <v>6121615644.454</v>
       </c>
       <c r="M21">
-        <v>107786658172.123</v>
+        <v>5841638947.146999</v>
       </c>
       <c r="N21">
-        <v>127007723396.892</v>
+        <v>6405202659.702999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>19685.693</v>
+      </c>
+      <c r="D22">
+        <v>18286.601</v>
+      </c>
+      <c r="E22">
+        <v>21098.23</v>
+      </c>
+      <c r="F22">
+        <v>30342.233</v>
+      </c>
+      <c r="G22">
+        <v>28621.749</v>
+      </c>
+      <c r="H22">
+        <v>32086.479</v>
+      </c>
+      <c r="I22">
+        <v>331502771.901</v>
+      </c>
+      <c r="J22">
+        <v>307893831.633</v>
+      </c>
+      <c r="K22">
+        <v>355303864.535</v>
+      </c>
+      <c r="L22">
+        <v>4035413844.521</v>
+      </c>
+      <c r="M22">
+        <v>3806579341.039</v>
+      </c>
+      <c r="N22">
+        <v>4267159979.048</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>124368.57</v>
+      </c>
+      <c r="D23">
+        <v>119826.286</v>
+      </c>
+      <c r="E23">
+        <v>128951.853</v>
+      </c>
+      <c r="F23">
+        <v>37888.488</v>
+      </c>
+      <c r="G23">
+        <v>36022.292</v>
+      </c>
+      <c r="H23">
+        <v>39787.26300000001</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>5039641313.578001</v>
+      </c>
+      <c r="M23">
+        <v>4791955674.33</v>
+      </c>
+      <c r="N23">
+        <v>5292052308.43</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>6153.139999999999</v>
+      </c>
+      <c r="D24">
+        <v>5843.130999999999</v>
+      </c>
+      <c r="E24">
+        <v>6470.463</v>
+      </c>
+      <c r="F24">
+        <v>11534.932</v>
+      </c>
+      <c r="G24">
+        <v>10941.091</v>
+      </c>
+      <c r="H24">
+        <v>12143.628</v>
+      </c>
+      <c r="I24">
+        <v>462752835.858</v>
+      </c>
+      <c r="J24">
+        <v>439406519.99</v>
+      </c>
+      <c r="K24">
+        <v>486523195.256</v>
+      </c>
+      <c r="L24">
+        <v>1534056555.389</v>
+      </c>
+      <c r="M24">
+        <v>1455050681.733</v>
+      </c>
+      <c r="N24">
+        <v>1615091038.32</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>99799.011</v>
+      </c>
+      <c r="D25">
+        <v>93299.829</v>
+      </c>
+      <c r="E25">
+        <v>106281.332</v>
+      </c>
+      <c r="F25">
+        <v>975153.5760000001</v>
+      </c>
+      <c r="G25">
+        <v>938203.0820000001</v>
+      </c>
+      <c r="H25">
+        <v>1012124.545</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>129701488512.029</v>
+      </c>
+      <c r="M25">
+        <v>124767884949.144</v>
+      </c>
+      <c r="N25">
+        <v>134646867717.17</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>113835.267</v>
+      </c>
+      <c r="D26">
+        <v>107518.176</v>
+      </c>
+      <c r="E26">
+        <v>120215.953</v>
+      </c>
+      <c r="F26">
+        <v>363653.718</v>
+      </c>
+      <c r="G26">
+        <v>347569.922</v>
+      </c>
+      <c r="H26">
+        <v>379826.657</v>
+      </c>
+      <c r="I26">
+        <v>1519689414.937</v>
+      </c>
+      <c r="J26">
+        <v>1433437578.864</v>
+      </c>
+      <c r="K26">
+        <v>1606815680.987</v>
+      </c>
+      <c r="L26">
+        <v>48365229372.65701</v>
+      </c>
+      <c r="M26">
+        <v>46225485608.541</v>
+      </c>
+      <c r="N26">
+        <v>50514419372.93201</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>91656.36199999999</v>
+      </c>
+      <c r="D27">
+        <v>87078.963</v>
+      </c>
+      <c r="E27">
+        <v>96242.459</v>
+      </c>
+      <c r="F27">
+        <v>334301.131</v>
+      </c>
+      <c r="G27">
+        <v>321646.803</v>
+      </c>
+      <c r="H27">
+        <v>346983.5860000001</v>
+      </c>
+      <c r="I27">
+        <v>1200762968.421</v>
+      </c>
+      <c r="J27">
+        <v>1140575522.608</v>
+      </c>
+      <c r="K27">
+        <v>1261653441.663</v>
+      </c>
+      <c r="L27">
+        <v>44460103001.008</v>
+      </c>
+      <c r="M27">
+        <v>42773136236.83199</v>
+      </c>
+      <c r="N27">
+        <v>46161825068.548</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>129813.178</v>
+      </c>
+      <c r="D28">
+        <v>123796.032</v>
+      </c>
+      <c r="E28">
+        <v>135859.693</v>
+      </c>
+      <c r="F28">
+        <v>445389.606</v>
+      </c>
+      <c r="G28">
+        <v>428713.22</v>
+      </c>
+      <c r="H28">
+        <v>462133.2990000001</v>
+      </c>
+      <c r="I28">
+        <v>1573600770.197</v>
+      </c>
+      <c r="J28">
+        <v>1496177412.441</v>
+      </c>
+      <c r="K28">
+        <v>1652109785.084</v>
+      </c>
+      <c r="L28">
+        <v>59245755427.52</v>
+      </c>
+      <c r="M28">
+        <v>57014066851.71</v>
+      </c>
+      <c r="N28">
+        <v>61487539117.01701</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>335304.807</v>
+      </c>
+      <c r="D29">
+        <v>318393.171</v>
+      </c>
+      <c r="E29">
+        <v>352318.105</v>
+      </c>
+      <c r="F29">
+        <v>1143344.455</v>
+      </c>
+      <c r="G29">
+        <v>1097929.945</v>
+      </c>
+      <c r="H29">
+        <v>1188943.542</v>
+      </c>
+      <c r="I29">
+        <v>4294053153.555</v>
+      </c>
+      <c r="J29">
+        <v>4070190513.913</v>
+      </c>
+      <c r="K29">
+        <v>4520578907.734</v>
+      </c>
+      <c r="L29">
+        <v>152071087801.185</v>
+      </c>
+      <c r="M29">
+        <v>146012688697.083</v>
+      </c>
+      <c r="N29">
+        <v>158163783558.4971</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>235505.796</v>
+      </c>
+      <c r="D30">
+        <v>225093.342</v>
+      </c>
+      <c r="E30">
+        <v>246036.773</v>
+      </c>
+      <c r="F30">
+        <v>168190.879</v>
+      </c>
+      <c r="G30">
+        <v>159726.863</v>
+      </c>
+      <c r="H30">
+        <v>176818.9969999999</v>
+      </c>
+      <c r="I30">
+        <v>4294053153.555</v>
+      </c>
+      <c r="J30">
+        <v>4070190513.913</v>
+      </c>
+      <c r="K30">
+        <v>4520578907.734</v>
+      </c>
+      <c r="L30">
+        <v>22369599289.156</v>
+      </c>
+      <c r="M30">
+        <v>21244803747.939</v>
+      </c>
+      <c r="N30">
+        <v>23516915841.327</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -1,21 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C687388-F5B8-DE4B-9FDC-EDF9B717C8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="22940" windowHeight="14720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>periurban</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +162,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +214,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +248,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +283,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,101 +459,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
         <v>34049.409</v>
       </c>
       <c r="D2">
-        <v>31641.343</v>
+        <v>31641.343000000001</v>
       </c>
       <c r="E2">
-        <v>36462.905</v>
+        <v>36462.904999999999</v>
       </c>
       <c r="F2">
         <v>308698.565</v>
@@ -453,7 +530,7 @@
         <v>295683.071</v>
       </c>
       <c r="H2">
-        <v>321730.497</v>
+        <v>321730.49699999997</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,34 +542,30 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>41056520139.482</v>
+        <v>41056520139.482002</v>
       </c>
       <c r="M2">
-        <v>39324435939.413</v>
+        <v>39324435939.413002</v>
       </c>
       <c r="N2">
-        <v>42788150076.078</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>42788150076.078003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>30892.621</v>
+        <v>30892.620999999999</v>
       </c>
       <c r="D3">
-        <v>28952.467</v>
+        <v>28952.467000000001</v>
       </c>
       <c r="E3">
-        <v>32820.011</v>
+        <v>32820.010999999999</v>
       </c>
       <c r="F3">
         <v>291691.451</v>
@@ -501,7 +574,7 @@
         <v>281081.82</v>
       </c>
       <c r="H3">
-        <v>302293.371</v>
+        <v>302293.37099999998</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,25 +586,21 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>38793008567.954</v>
+        <v>38793008567.954002</v>
       </c>
       <c r="M3">
-        <v>37378154366.943</v>
+        <v>37378154366.943001</v>
       </c>
       <c r="N3">
-        <v>40217566983.298</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>40217566983.297997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>34856.981</v>
@@ -540,16 +609,16 @@
         <v>32706.019</v>
       </c>
       <c r="E4">
-        <v>36998.416</v>
+        <v>36998.415999999997</v>
       </c>
       <c r="F4">
         <v>374763.56</v>
       </c>
       <c r="G4">
-        <v>361438.191</v>
+        <v>361438.19099999999</v>
       </c>
       <c r="H4">
-        <v>388100.677</v>
+        <v>388100.67700000003</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,34 +630,30 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>49851959804.593</v>
+        <v>49851959804.593002</v>
       </c>
       <c r="M4">
-        <v>48065294642.788</v>
+        <v>48065294642.788002</v>
       </c>
       <c r="N4">
-        <v>51641150657.794</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>51641150657.793999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>19522.368</v>
+        <v>19522.367999999999</v>
       </c>
       <c r="D5">
-        <v>18429.798</v>
+        <v>18429.797999999999</v>
       </c>
       <c r="E5">
-        <v>20629.758</v>
+        <v>20629.758000000002</v>
       </c>
       <c r="F5">
         <v>15535.261</v>
@@ -603,43 +668,39 @@
         <v>1087509723.915</v>
       </c>
       <c r="J5">
-        <v>1026502557.435</v>
+        <v>1026502557.4349999</v>
       </c>
       <c r="K5">
         <v>1148957113.77</v>
       </c>
       <c r="L5">
-        <v>2066150897.081</v>
+        <v>2066150897.0810001</v>
       </c>
       <c r="M5">
         <v>1962729276.563</v>
       </c>
       <c r="N5">
-        <v>2170818141.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>2170818141.9499998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>15629.423</v>
+        <v>15629.423000000001</v>
       </c>
       <c r="D6">
         <v>14864.087</v>
       </c>
       <c r="E6">
-        <v>16403.455</v>
+        <v>16403.455000000002</v>
       </c>
       <c r="F6">
-        <v>12847.594</v>
+        <v>12847.593999999999</v>
       </c>
       <c r="G6">
         <v>12273.394</v>
@@ -648,46 +709,42 @@
         <v>13431.71</v>
       </c>
       <c r="I6">
-        <v>870706606.089</v>
+        <v>870706606.08899999</v>
       </c>
       <c r="J6">
-        <v>828088414.568</v>
+        <v>828088414.56799996</v>
       </c>
       <c r="K6">
-        <v>913804891.925</v>
+        <v>913804891.92499995</v>
       </c>
       <c r="L6">
-        <v>1708827181.884</v>
+        <v>1708827181.8840001</v>
       </c>
       <c r="M6">
         <v>1632379050.51</v>
       </c>
       <c r="N6">
-        <v>1786480557.537</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>1786480557.5369999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>19540.313</v>
+        <v>19540.312999999998</v>
       </c>
       <c r="D7">
         <v>18587.38</v>
       </c>
       <c r="E7">
-        <v>20505.26</v>
+        <v>20505.259999999998</v>
       </c>
       <c r="F7">
-        <v>17642.669</v>
+        <v>17642.669000000002</v>
       </c>
       <c r="G7">
         <v>16890.77</v>
@@ -696,37 +753,33 @@
         <v>18401.59</v>
       </c>
       <c r="I7">
-        <v>1088430310.521</v>
+        <v>1088430310.5209999</v>
       </c>
       <c r="J7">
-        <v>1035056644.269</v>
+        <v>1035056644.2690001</v>
       </c>
       <c r="K7">
-        <v>1142498325.722</v>
+        <v>1142498325.7219999</v>
       </c>
       <c r="L7">
-        <v>2346637565.489</v>
+        <v>2346637565.4889998</v>
       </c>
       <c r="M7">
-        <v>2246530620.074</v>
+        <v>2246530620.0739999</v>
       </c>
       <c r="N7">
-        <v>2447903960.216</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>2447903960.2160001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>10515.488</v>
+        <v>10515.487999999999</v>
       </c>
       <c r="D8">
         <v>10003.627</v>
@@ -744,13 +797,13 @@
         <v>14384.945</v>
       </c>
       <c r="I8">
-        <v>155674252.981</v>
+        <v>155674252.98100001</v>
       </c>
       <c r="J8">
         <v>148116429.745</v>
       </c>
       <c r="K8">
-        <v>163421607.115</v>
+        <v>163421607.11500001</v>
       </c>
       <c r="L8">
         <v>1805043633.704</v>
@@ -759,40 +812,36 @@
         <v>1701699773.74</v>
       </c>
       <c r="N8">
-        <v>1912896347.35</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>1912896347.3499999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
-        <v>7888.195</v>
+        <v>7888.1949999999997</v>
       </c>
       <c r="D9">
-        <v>7550.356</v>
+        <v>7550.3559999999998</v>
       </c>
       <c r="E9">
-        <v>8227.514999999999</v>
+        <v>8227.5149999999994</v>
       </c>
       <c r="F9">
         <v>10158.23</v>
       </c>
       <c r="G9">
-        <v>9657.742</v>
+        <v>9657.7420000000002</v>
       </c>
       <c r="H9">
         <v>10670.856</v>
       </c>
       <c r="I9">
-        <v>116793443.135</v>
+        <v>116793443.13500001</v>
       </c>
       <c r="J9">
         <v>111818763.883</v>
@@ -801,97 +850,89 @@
         <v>121848043.361</v>
       </c>
       <c r="L9">
-        <v>1351001949.337</v>
+        <v>1351001949.3369999</v>
       </c>
       <c r="M9">
-        <v>1284083548.561</v>
+        <v>1284083548.5610001</v>
       </c>
       <c r="N9">
         <v>1419347434.618</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
         <v>12202.606</v>
       </c>
       <c r="D10">
-        <v>11702.076</v>
+        <v>11702.075999999999</v>
       </c>
       <c r="E10">
-        <v>12710.426</v>
+        <v>12710.425999999999</v>
       </c>
       <c r="F10">
-        <v>18668.542</v>
+        <v>18668.542000000001</v>
       </c>
       <c r="G10">
-        <v>17767.994</v>
+        <v>17767.993999999999</v>
       </c>
       <c r="H10">
-        <v>19590.188</v>
+        <v>19590.187999999998</v>
       </c>
       <c r="I10">
         <v>180683209.155</v>
       </c>
       <c r="J10">
-        <v>173307352.39</v>
+        <v>173307352.38999999</v>
       </c>
       <c r="K10">
-        <v>188221866.05</v>
+        <v>188221866.05000001</v>
       </c>
       <c r="L10">
-        <v>2482826348.173</v>
+        <v>2482826348.1729999</v>
       </c>
       <c r="M10">
-        <v>2363795781.389</v>
+        <v>2363795781.3889999</v>
       </c>
       <c r="N10">
-        <v>2605166073.858</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>2605166073.8579998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>2061.315</v>
+        <v>2061.3150000000001</v>
       </c>
       <c r="D11">
-        <v>1947.545</v>
+        <v>1947.5450000000001</v>
       </c>
       <c r="E11">
-        <v>2179.217</v>
+        <v>2179.2170000000001</v>
       </c>
       <c r="F11">
-        <v>3637.914</v>
+        <v>3637.9140000000002</v>
       </c>
       <c r="G11">
         <v>3432.431</v>
       </c>
       <c r="H11">
-        <v>3851.968</v>
+        <v>3851.9679999999998</v>
       </c>
       <c r="I11">
-        <v>155028017.311</v>
+        <v>155028017.31099999</v>
       </c>
       <c r="J11">
-        <v>146404317.481</v>
+        <v>146404317.48100001</v>
       </c>
       <c r="K11">
         <v>163824978.991</v>
@@ -900,22 +941,18 @@
         <v>483855512.778</v>
       </c>
       <c r="M11">
-        <v>456413429.3</v>
+        <v>456413429.30000001</v>
       </c>
       <c r="N11">
-        <v>512324804.105</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>512324804.10500002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
         <v>1589.586</v>
@@ -924,16 +961,16 @@
         <v>1509.83</v>
       </c>
       <c r="E12">
-        <v>1670.534</v>
+        <v>1670.5340000000001</v>
       </c>
       <c r="F12">
-        <v>2817.139</v>
+        <v>2817.1390000000001</v>
       </c>
       <c r="G12">
-        <v>2673.513</v>
+        <v>2673.5129999999999</v>
       </c>
       <c r="H12">
-        <v>2963.291</v>
+        <v>2963.2910000000002</v>
       </c>
       <c r="I12">
         <v>119551979.618</v>
@@ -942,100 +979,92 @@
         <v>113582967.64</v>
       </c>
       <c r="K12">
-        <v>125621285.018</v>
+        <v>125621285.01800001</v>
       </c>
       <c r="L12">
-        <v>374643304.057</v>
+        <v>374643304.05699998</v>
       </c>
       <c r="M12">
         <v>355596299.421</v>
       </c>
       <c r="N12">
-        <v>394125231.016</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>394125231.01599997</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
         <v>2502.239</v>
       </c>
       <c r="D13">
-        <v>2385.756</v>
+        <v>2385.7559999999999</v>
       </c>
       <c r="E13">
         <v>2620.712</v>
       </c>
       <c r="F13">
-        <v>5079.879</v>
+        <v>5079.8789999999999</v>
       </c>
       <c r="G13">
-        <v>4835.147</v>
+        <v>4835.1469999999999</v>
       </c>
       <c r="H13">
-        <v>5328.369</v>
+        <v>5328.3689999999997</v>
       </c>
       <c r="I13">
-        <v>188172838.929</v>
+        <v>188172838.92899999</v>
       </c>
       <c r="J13">
-        <v>179419234.869</v>
+        <v>179419234.86899999</v>
       </c>
       <c r="K13">
-        <v>197076931.247</v>
+        <v>197076931.24700001</v>
       </c>
       <c r="L13">
-        <v>675557738.554</v>
+        <v>675557738.55400002</v>
       </c>
       <c r="M13">
-        <v>643040953.012</v>
+        <v>643040953.01199996</v>
       </c>
       <c r="N13">
         <v>708641003.199</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>7213.704</v>
+        <v>7213.7039999999997</v>
       </c>
       <c r="D14">
-        <v>6674.728</v>
+        <v>6674.7280000000001</v>
       </c>
       <c r="E14">
-        <v>7755.744</v>
+        <v>7755.7439999999997</v>
       </c>
       <c r="F14">
         <v>10776.984</v>
       </c>
       <c r="G14">
-        <v>10110.024</v>
+        <v>10110.023999999999</v>
       </c>
       <c r="H14">
-        <v>11452.362</v>
+        <v>11452.361999999999</v>
       </c>
       <c r="I14">
         <v>121477420.73</v>
       </c>
       <c r="J14">
-        <v>112414274.203</v>
+        <v>112414274.20299999</v>
       </c>
       <c r="K14">
         <v>130611981.111</v>
@@ -1044,52 +1073,48 @@
         <v>1433187243.799</v>
       </c>
       <c r="M14">
-        <v>1344550931.643</v>
+        <v>1344550931.6429999</v>
       </c>
       <c r="N14">
-        <v>1522907246.314</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>1522907246.3139999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
         <v>5565.41</v>
       </c>
       <c r="D15">
-        <v>5172.745</v>
+        <v>5172.7449999999999</v>
       </c>
       <c r="E15">
-        <v>5963.294</v>
+        <v>5963.2939999999999</v>
       </c>
       <c r="F15">
-        <v>8304.186</v>
+        <v>8304.1859999999997</v>
       </c>
       <c r="G15">
         <v>7874.326</v>
       </c>
       <c r="H15">
-        <v>8737.806</v>
+        <v>8737.8060000000005</v>
       </c>
       <c r="I15">
-        <v>93710939.579</v>
+        <v>93710939.578999996</v>
       </c>
       <c r="J15">
-        <v>87085376.517</v>
+        <v>87085376.517000005</v>
       </c>
       <c r="K15">
         <v>100379221.359</v>
       </c>
       <c r="L15">
-        <v>1104282255.817</v>
+        <v>1104282255.8169999</v>
       </c>
       <c r="M15">
         <v>1047514511.451</v>
@@ -1098,22 +1123,18 @@
         <v>1162164992.642</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>6906.579</v>
+        <v>6906.5789999999997</v>
       </c>
       <c r="D16">
-        <v>6439.128</v>
+        <v>6439.1279999999997</v>
       </c>
       <c r="E16">
         <v>7379.192</v>
@@ -1122,13 +1143,13 @@
         <v>11261.063</v>
       </c>
       <c r="G16">
-        <v>10637.399</v>
+        <v>10637.398999999999</v>
       </c>
       <c r="H16">
         <v>11896.311</v>
       </c>
       <c r="I16">
-        <v>116314411.592</v>
+        <v>116314411.59199999</v>
       </c>
       <c r="J16">
         <v>108394180.913</v>
@@ -1140,37 +1161,33 @@
         <v>1497944344.905</v>
       </c>
       <c r="M16">
-        <v>1414513897.945</v>
+        <v>1414513897.9449999</v>
       </c>
       <c r="N16">
         <v>1582087740.092</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17">
         <v>40472.983</v>
       </c>
       <c r="D17">
-        <v>38821.135</v>
+        <v>38821.135000000002</v>
       </c>
       <c r="E17">
-        <v>42148.516</v>
+        <v>42148.516000000003</v>
       </c>
       <c r="F17">
         <v>11432.064</v>
       </c>
       <c r="G17">
-        <v>10792.565</v>
+        <v>10792.565000000001</v>
       </c>
       <c r="H17">
         <v>12084.547</v>
@@ -1194,34 +1211,30 @@
         <v>1607322757.135</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
         <v>30091.127</v>
       </c>
       <c r="D18">
-        <v>29029.478</v>
+        <v>29029.477999999999</v>
       </c>
       <c r="E18">
         <v>31157.65</v>
       </c>
       <c r="F18">
-        <v>8482.531000000001</v>
+        <v>8482.5310000000009</v>
       </c>
       <c r="G18">
-        <v>8086.008</v>
+        <v>8086.0079999999998</v>
       </c>
       <c r="H18">
-        <v>8886.552</v>
+        <v>8886.5519999999997</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,43 +1246,39 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1128339741.959</v>
+        <v>1128339741.9590001</v>
       </c>
       <c r="M18">
-        <v>1075408459.946</v>
+        <v>1075408459.9460001</v>
       </c>
       <c r="N18">
         <v>1182139869.437</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
         <v>53804.46</v>
       </c>
       <c r="D19">
-        <v>51975.673</v>
+        <v>51975.673000000003</v>
       </c>
       <c r="E19">
-        <v>55645.687</v>
+        <v>55645.686999999998</v>
       </c>
       <c r="F19">
         <v>17973.893</v>
       </c>
       <c r="G19">
-        <v>17143.719</v>
+        <v>17143.719000000001</v>
       </c>
       <c r="H19">
-        <v>18816.164</v>
+        <v>18816.164000000001</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,127 +1290,115 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2390829625.806</v>
+        <v>2390829625.8060002</v>
       </c>
       <c r="M19">
-        <v>2280890956.502</v>
+        <v>2280890956.5019999</v>
       </c>
       <c r="N19">
-        <v>2502589681.858</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>2502589681.8579998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>30606.289</v>
+        <v>30606.289000000001</v>
       </c>
       <c r="D20">
-        <v>29256.059</v>
+        <v>29256.059000000001</v>
       </c>
       <c r="E20">
-        <v>31977.754</v>
+        <v>31977.754000000001</v>
       </c>
       <c r="F20">
-        <v>42399.702</v>
+        <v>42399.701999999997</v>
       </c>
       <c r="G20">
-        <v>40221.583</v>
+        <v>40221.582999999999</v>
       </c>
       <c r="H20">
-        <v>44645.989</v>
+        <v>44645.989000000001</v>
       </c>
       <c r="I20">
-        <v>453150905.271</v>
+        <v>453150905.27100003</v>
       </c>
       <c r="J20">
-        <v>433242546.018</v>
+        <v>433242546.01800001</v>
       </c>
       <c r="K20">
-        <v>473491516.526</v>
+        <v>473491516.52600002</v>
       </c>
       <c r="L20">
-        <v>5638871931.214</v>
+        <v>5638871931.2139997</v>
       </c>
       <c r="M20">
-        <v>5349579103.690001</v>
+        <v>5349579103.6900005</v>
       </c>
       <c r="N20">
-        <v>5937409855.826</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>5937409855.8260002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>54692.10399999999</v>
+        <v>54692.103999999992</v>
       </c>
       <c r="D21">
-        <v>51881.265</v>
+        <v>51881.264999999999</v>
       </c>
       <c r="E21">
-        <v>57538.473</v>
+        <v>57538.472999999998</v>
       </c>
       <c r="F21">
-        <v>46025.524</v>
+        <v>46025.523999999998</v>
       </c>
       <c r="G21">
-        <v>43920.148</v>
+        <v>43920.148000000001</v>
       </c>
       <c r="H21">
-        <v>48155.638</v>
+        <v>48155.637999999999</v>
       </c>
       <c r="I21">
-        <v>3046646640.525</v>
+        <v>3046646640.5250001</v>
       </c>
       <c r="J21">
-        <v>2889647616.272</v>
+        <v>2889647616.2719998</v>
       </c>
       <c r="K21">
-        <v>3205260331.417</v>
+        <v>3205260331.4169998</v>
       </c>
       <c r="L21">
-        <v>6121615644.454</v>
+        <v>6121615644.4540005</v>
       </c>
       <c r="M21">
-        <v>5841638947.146999</v>
+        <v>5841638947.1469994</v>
       </c>
       <c r="N21">
-        <v>6405202659.702999</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>6405202659.7029991</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>19685.693</v>
+        <v>19685.692999999999</v>
       </c>
       <c r="D22">
-        <v>18286.601</v>
+        <v>18286.600999999999</v>
       </c>
       <c r="E22">
         <v>21098.23</v>
@@ -1413,55 +1410,51 @@
         <v>28621.749</v>
       </c>
       <c r="H22">
-        <v>32086.479</v>
+        <v>32086.478999999999</v>
       </c>
       <c r="I22">
-        <v>331502771.901</v>
+        <v>331502771.90100002</v>
       </c>
       <c r="J22">
-        <v>307893831.633</v>
+        <v>307893831.63300002</v>
       </c>
       <c r="K22">
-        <v>355303864.535</v>
+        <v>355303864.53500003</v>
       </c>
       <c r="L22">
-        <v>4035413844.521</v>
+        <v>4035413844.5209999</v>
       </c>
       <c r="M22">
         <v>3806579341.039</v>
       </c>
       <c r="N22">
-        <v>4267159979.048</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>4267159979.0479999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23">
         <v>124368.57</v>
       </c>
       <c r="D23">
-        <v>119826.286</v>
+        <v>119826.28599999999</v>
       </c>
       <c r="E23">
         <v>128951.853</v>
       </c>
       <c r="F23">
-        <v>37888.488</v>
+        <v>37888.487999999998</v>
       </c>
       <c r="G23">
-        <v>36022.292</v>
+        <v>36022.292000000001</v>
       </c>
       <c r="H23">
-        <v>39787.26300000001</v>
+        <v>39787.263000000014</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1476,85 +1469,77 @@
         <v>5039641313.578001</v>
       </c>
       <c r="M23">
-        <v>4791955674.33</v>
+        <v>4791955674.3299999</v>
       </c>
       <c r="N23">
-        <v>5292052308.43</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>5292052308.4300003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>6153.139999999999</v>
+        <v>6153.1399999999994</v>
       </c>
       <c r="D24">
-        <v>5843.130999999999</v>
+        <v>5843.1309999999994</v>
       </c>
       <c r="E24">
-        <v>6470.463</v>
+        <v>6470.4629999999997</v>
       </c>
       <c r="F24">
-        <v>11534.932</v>
+        <v>11534.932000000001</v>
       </c>
       <c r="G24">
         <v>10941.091</v>
       </c>
       <c r="H24">
-        <v>12143.628</v>
+        <v>12143.628000000001</v>
       </c>
       <c r="I24">
-        <v>462752835.858</v>
+        <v>462752835.85799998</v>
       </c>
       <c r="J24">
-        <v>439406519.99</v>
+        <v>439406519.99000001</v>
       </c>
       <c r="K24">
-        <v>486523195.256</v>
+        <v>486523195.25599998</v>
       </c>
       <c r="L24">
-        <v>1534056555.389</v>
+        <v>1534056555.3889999</v>
       </c>
       <c r="M24">
         <v>1455050681.733</v>
       </c>
       <c r="N24">
-        <v>1615091038.32</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>1615091038.3199999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>99799.011</v>
+        <v>99799.010999999999</v>
       </c>
       <c r="D25">
-        <v>93299.829</v>
+        <v>93299.828999999998</v>
       </c>
       <c r="E25">
-        <v>106281.332</v>
+        <v>106281.33199999999</v>
       </c>
       <c r="F25">
-        <v>975153.5760000001</v>
+        <v>975153.57600000012</v>
       </c>
       <c r="G25">
-        <v>938203.0820000001</v>
+        <v>938203.08200000005</v>
       </c>
       <c r="H25">
         <v>1012124.545</v>
@@ -1569,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>129701488512.029</v>
+        <v>129701488512.02901</v>
       </c>
       <c r="M25">
         <v>124767884949.144</v>
@@ -1578,82 +1563,74 @@
         <v>134646867717.17</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>113835.267</v>
+        <v>113835.26700000001</v>
       </c>
       <c r="D26">
-        <v>107518.176</v>
+        <v>107518.17600000001</v>
       </c>
       <c r="E26">
-        <v>120215.953</v>
+        <v>120215.95299999999</v>
       </c>
       <c r="F26">
-        <v>363653.718</v>
+        <v>363653.71799999999</v>
       </c>
       <c r="G26">
-        <v>347569.922</v>
+        <v>347569.92200000002</v>
       </c>
       <c r="H26">
-        <v>379826.657</v>
+        <v>379826.65700000001</v>
       </c>
       <c r="I26">
         <v>1519689414.937</v>
       </c>
       <c r="J26">
-        <v>1433437578.864</v>
+        <v>1433437578.8640001</v>
       </c>
       <c r="K26">
         <v>1606815680.987</v>
       </c>
       <c r="L26">
-        <v>48365229372.65701</v>
+        <v>48365229372.657013</v>
       </c>
       <c r="M26">
         <v>46225485608.541</v>
       </c>
       <c r="N26">
-        <v>50514419372.93201</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>50514419372.932007</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>91656.36199999999</v>
+        <v>91656.361999999994</v>
       </c>
       <c r="D27">
-        <v>87078.963</v>
+        <v>87078.963000000003</v>
       </c>
       <c r="E27">
-        <v>96242.459</v>
+        <v>96242.459000000003</v>
       </c>
       <c r="F27">
-        <v>334301.131</v>
+        <v>334301.13099999999</v>
       </c>
       <c r="G27">
-        <v>321646.803</v>
+        <v>321646.80300000001</v>
       </c>
       <c r="H27">
-        <v>346983.5860000001</v>
+        <v>346983.58600000013</v>
       </c>
       <c r="I27">
         <v>1200762968.421</v>
@@ -1662,46 +1639,42 @@
         <v>1140575522.608</v>
       </c>
       <c r="K27">
-        <v>1261653441.663</v>
+        <v>1261653441.6630001</v>
       </c>
       <c r="L27">
-        <v>44460103001.008</v>
+        <v>44460103001.008003</v>
       </c>
       <c r="M27">
-        <v>42773136236.83199</v>
+        <v>42773136236.831993</v>
       </c>
       <c r="N27">
-        <v>46161825068.548</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>46161825068.547997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
       </c>
       <c r="C28">
         <v>129813.178</v>
       </c>
       <c r="D28">
-        <v>123796.032</v>
+        <v>123796.03200000001</v>
       </c>
       <c r="E28">
         <v>135859.693</v>
       </c>
       <c r="F28">
-        <v>445389.606</v>
+        <v>445389.60600000003</v>
       </c>
       <c r="G28">
         <v>428713.22</v>
       </c>
       <c r="H28">
-        <v>462133.2990000001</v>
+        <v>462133.29900000012</v>
       </c>
       <c r="I28">
         <v>1573600770.197</v>
@@ -1710,76 +1683,68 @@
         <v>1496177412.441</v>
       </c>
       <c r="K28">
-        <v>1652109785.084</v>
+        <v>1652109785.0840001</v>
       </c>
       <c r="L28">
-        <v>59245755427.52</v>
+        <v>59245755427.519997</v>
       </c>
       <c r="M28">
-        <v>57014066851.71</v>
+        <v>57014066851.709999</v>
       </c>
       <c r="N28">
-        <v>61487539117.01701</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>61487539117.017014</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>335304.807</v>
+        <v>335304.80699999997</v>
       </c>
       <c r="D29">
-        <v>318393.171</v>
+        <v>318393.17099999997</v>
       </c>
       <c r="E29">
-        <v>352318.105</v>
+        <v>352318.10499999998</v>
       </c>
       <c r="F29">
-        <v>1143344.455</v>
+        <v>1143344.4550000001</v>
       </c>
       <c r="G29">
-        <v>1097929.945</v>
+        <v>1097929.9450000001</v>
       </c>
       <c r="H29">
-        <v>1188943.542</v>
+        <v>1188943.5419999999</v>
       </c>
       <c r="I29">
-        <v>4294053153.555</v>
+        <v>4294053153.5549998</v>
       </c>
       <c r="J29">
-        <v>4070190513.913</v>
+        <v>4070190513.9130001</v>
       </c>
       <c r="K29">
-        <v>4520578907.734</v>
+        <v>4520578907.7340002</v>
       </c>
       <c r="L29">
         <v>152071087801.185</v>
       </c>
       <c r="M29">
-        <v>146012688697.083</v>
+        <v>146012688697.08301</v>
       </c>
       <c r="N29">
         <v>158163783558.4971</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
       </c>
       <c r="C30">
         <v>235505.796</v>
@@ -1788,31 +1753,31 @@
         <v>225093.342</v>
       </c>
       <c r="E30">
-        <v>246036.773</v>
+        <v>246036.77299999999</v>
       </c>
       <c r="F30">
-        <v>168190.879</v>
+        <v>168190.87899999999</v>
       </c>
       <c r="G30">
-        <v>159726.863</v>
+        <v>159726.86300000001</v>
       </c>
       <c r="H30">
-        <v>176818.9969999999</v>
+        <v>176818.99699999989</v>
       </c>
       <c r="I30">
-        <v>4294053153.555</v>
+        <v>4294053153.5549998</v>
       </c>
       <c r="J30">
-        <v>4070190513.913</v>
+        <v>4070190513.9130001</v>
       </c>
       <c r="K30">
-        <v>4520578907.734</v>
+        <v>4520578907.7340002</v>
       </c>
       <c r="L30">
-        <v>22369599289.156</v>
+        <v>22369599289.155998</v>
       </c>
       <c r="M30">
-        <v>21244803747.939</v>
+        <v>21244803747.938999</v>
       </c>
       <c r="N30">
         <v>23516915841.327</v>

--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -1,120 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C687388-F5B8-DE4B-9FDC-EDF9B717C8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="22940" windowHeight="14720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>area_type</t>
-  </si>
-  <si>
-    <t>tot_cases</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>periurban</t>
-  </si>
-  <si>
-    <t>rural</t>
-  </si>
-  <si>
-    <t>urban</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Morbidity</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -214,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -248,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -283,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -459,78 +350,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>area_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C2">
-        <v>34049.409</v>
+        <v>36806.308</v>
       </c>
       <c r="D2">
-        <v>31641.343000000001</v>
+        <v>34220.327</v>
       </c>
       <c r="E2">
-        <v>36462.904999999999</v>
+        <v>39394.16</v>
       </c>
       <c r="F2">
-        <v>308698.565</v>
+        <v>341516.823</v>
       </c>
       <c r="G2">
-        <v>295683.071</v>
+        <v>326940.01</v>
       </c>
       <c r="H2">
-        <v>321730.49699999997</v>
+        <v>356098.202</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -542,39 +465,43 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>41056520139.482002</v>
+        <v>45422491789.039</v>
       </c>
       <c r="M2">
-        <v>39324435939.413002</v>
+        <v>43480886742.723</v>
       </c>
       <c r="N2">
-        <v>42788150076.078003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
+        <v>47365394777.025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C3">
-        <v>30892.620999999999</v>
+        <v>33267.112</v>
       </c>
       <c r="D3">
-        <v>28952.467000000001</v>
+        <v>31175.505</v>
       </c>
       <c r="E3">
-        <v>32820.010999999999</v>
+        <v>35346.168</v>
       </c>
       <c r="F3">
-        <v>291691.451</v>
+        <v>327423.941</v>
       </c>
       <c r="G3">
-        <v>281081.82</v>
+        <v>314910.033</v>
       </c>
       <c r="H3">
-        <v>302293.37099999998</v>
+        <v>339916.537</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -586,39 +513,43 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>38793008567.954002</v>
+        <v>43542526515.595</v>
       </c>
       <c r="M3">
-        <v>37378154366.943001</v>
+        <v>41879092249.947</v>
       </c>
       <c r="N3">
-        <v>40217566983.297997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+        <v>45221777852.946</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C4">
-        <v>34856.981</v>
+        <v>40418.99</v>
       </c>
       <c r="D4">
-        <v>32706.019</v>
+        <v>37938.566</v>
       </c>
       <c r="E4">
-        <v>36998.415999999997</v>
+        <v>42889.961</v>
       </c>
       <c r="F4">
-        <v>374763.56</v>
+        <v>442385.072</v>
       </c>
       <c r="G4">
-        <v>361438.19099999999</v>
+        <v>426436.206</v>
       </c>
       <c r="H4">
-        <v>388100.67700000003</v>
+        <v>458349.749</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -630,567 +561,619 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>49851959804.593002</v>
+        <v>58846863486.456</v>
       </c>
       <c r="M4">
-        <v>48065294642.788002</v>
+        <v>56715847026.923</v>
       </c>
       <c r="N4">
-        <v>51641150657.793999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
+        <v>60986092072.639</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C5">
-        <v>19522.367999999999</v>
+        <v>23697.925</v>
       </c>
       <c r="D5">
-        <v>18429.797999999999</v>
+        <v>22335.302</v>
       </c>
       <c r="E5">
-        <v>20629.758000000002</v>
+        <v>25071.976</v>
       </c>
       <c r="F5">
-        <v>15535.261</v>
+        <v>19319.041</v>
       </c>
       <c r="G5">
-        <v>14755.984</v>
+        <v>18308.509</v>
       </c>
       <c r="H5">
-        <v>16322.338</v>
+        <v>20338.657</v>
       </c>
       <c r="I5">
-        <v>1087509723.915</v>
+        <v>1320056785.603</v>
       </c>
       <c r="J5">
-        <v>1026502557.4349999</v>
+        <v>1243989370.475</v>
       </c>
       <c r="K5">
-        <v>1148957113.77</v>
+        <v>1396841057.494</v>
       </c>
       <c r="L5">
-        <v>2066150897.0810001</v>
+        <v>2569568285.112</v>
       </c>
       <c r="M5">
-        <v>1962729276.563</v>
+        <v>2435084861.457</v>
       </c>
       <c r="N5">
-        <v>2170818141.9499998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
+        <v>2704838419.696</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C6">
-        <v>15629.423000000001</v>
+        <v>19304.705</v>
       </c>
       <c r="D6">
-        <v>14864.087</v>
+        <v>18252.853</v>
       </c>
       <c r="E6">
-        <v>16403.455000000002</v>
+        <v>20371.584</v>
       </c>
       <c r="F6">
-        <v>12847.593999999999</v>
+        <v>16592.355</v>
       </c>
       <c r="G6">
-        <v>12273.394</v>
+        <v>15730.247</v>
       </c>
       <c r="H6">
-        <v>13431.71</v>
+        <v>17473.909</v>
       </c>
       <c r="I6">
-        <v>870706606.08899999</v>
+        <v>1075464482.121</v>
       </c>
       <c r="J6">
-        <v>828088414.56799996</v>
+        <v>1016486063.516</v>
       </c>
       <c r="K6">
-        <v>913804891.92499995</v>
+        <v>1134949585.895</v>
       </c>
       <c r="L6">
-        <v>1708827181.8840001</v>
+        <v>2207280545.385</v>
       </c>
       <c r="M6">
-        <v>1632379050.51</v>
+        <v>2091761912.935</v>
       </c>
       <c r="N6">
-        <v>1786480557.5369999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
+        <v>2323870695.911</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C7">
-        <v>19540.312999999998</v>
+        <v>27249.807</v>
       </c>
       <c r="D7">
-        <v>18587.38</v>
+        <v>25872.542</v>
       </c>
       <c r="E7">
-        <v>20505.259999999998</v>
+        <v>28637.728</v>
       </c>
       <c r="F7">
-        <v>17642.669000000002</v>
+        <v>25227.159</v>
       </c>
       <c r="G7">
-        <v>16890.77</v>
+        <v>24091.991</v>
       </c>
       <c r="H7">
-        <v>18401.59</v>
+        <v>26372.742</v>
       </c>
       <c r="I7">
-        <v>1088430310.5209999</v>
+        <v>1518052981.053</v>
       </c>
       <c r="J7">
-        <v>1035056644.2690001</v>
+        <v>1440886429.863</v>
       </c>
       <c r="K7">
-        <v>1142498325.7219999</v>
+        <v>1595682985.208</v>
       </c>
       <c r="L7">
-        <v>2346637565.4889998</v>
+        <v>3355201911.441</v>
       </c>
       <c r="M7">
-        <v>2246530620.0739999</v>
+        <v>3204452471.781</v>
       </c>
       <c r="N7">
-        <v>2447903960.2160001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
+        <v>3507007826.428</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C8">
-        <v>10515.487999999999</v>
+        <v>13887.759</v>
       </c>
       <c r="D8">
-        <v>10003.627</v>
+        <v>13084.311</v>
       </c>
       <c r="E8">
-        <v>11039.813</v>
+        <v>14712.902</v>
       </c>
       <c r="F8">
-        <v>13572.93</v>
+        <v>18478.91</v>
       </c>
       <c r="G8">
-        <v>12795.847</v>
+        <v>17118.839</v>
       </c>
       <c r="H8">
-        <v>14384.945</v>
+        <v>19945.991</v>
       </c>
       <c r="I8">
-        <v>155674252.98100001</v>
+        <v>205613521.802</v>
       </c>
       <c r="J8">
-        <v>148116429.745</v>
+        <v>193706414.515</v>
       </c>
       <c r="K8">
-        <v>163421607.11500001</v>
+        <v>217783810.914</v>
       </c>
       <c r="L8">
-        <v>1805043633.704</v>
+        <v>2457606556.362</v>
       </c>
       <c r="M8">
-        <v>1701699773.74</v>
+        <v>2276466284.238</v>
       </c>
       <c r="N8">
-        <v>1912896347.3499999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
+        <v>2652927959.668</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C9">
-        <v>7888.1949999999997</v>
+        <v>10935.385</v>
       </c>
       <c r="D9">
-        <v>7550.3559999999998</v>
+        <v>10307.172</v>
       </c>
       <c r="E9">
-        <v>8227.5149999999994</v>
+        <v>11582.142</v>
       </c>
       <c r="F9">
-        <v>10158.23</v>
+        <v>14801.262</v>
       </c>
       <c r="G9">
-        <v>9657.7420000000002</v>
+        <v>13782.053</v>
       </c>
       <c r="H9">
-        <v>10670.856</v>
+        <v>15865.077</v>
       </c>
       <c r="I9">
-        <v>116793443.13500001</v>
+        <v>161916543.395</v>
       </c>
       <c r="J9">
-        <v>111818763.883</v>
+        <v>152619159.253</v>
       </c>
       <c r="K9">
-        <v>121848043.361</v>
+        <v>171561934.507</v>
       </c>
       <c r="L9">
-        <v>1351001949.3369999</v>
+        <v>1968572551.649</v>
       </c>
       <c r="M9">
-        <v>1284083548.5610001</v>
+        <v>1832807231.113</v>
       </c>
       <c r="N9">
-        <v>1419347434.618</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
+        <v>2111156946.874</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C10">
-        <v>12202.606</v>
+        <v>20185.028</v>
       </c>
       <c r="D10">
-        <v>11702.075999999999</v>
+        <v>19168.591</v>
       </c>
       <c r="E10">
-        <v>12710.425999999999</v>
+        <v>21219.991</v>
       </c>
       <c r="F10">
-        <v>18668.542000000001</v>
+        <v>31883.471</v>
       </c>
       <c r="G10">
-        <v>17767.993999999999</v>
+        <v>29961.68</v>
       </c>
       <c r="H10">
-        <v>19590.187999999998</v>
+        <v>33863.238</v>
       </c>
       <c r="I10">
-        <v>180683209.155</v>
+        <v>298859017.298</v>
       </c>
       <c r="J10">
-        <v>173307352.38999999</v>
+        <v>283878779.463</v>
       </c>
       <c r="K10">
-        <v>188221866.05000001</v>
+        <v>314277325.032</v>
       </c>
       <c r="L10">
-        <v>2482826348.1729999</v>
+        <v>4240090894.026</v>
       </c>
       <c r="M10">
-        <v>2363795781.3889999</v>
+        <v>3986080225.475</v>
       </c>
       <c r="N10">
-        <v>2605166073.8579998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
+        <v>4502223239.245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C11">
-        <v>2061.3150000000001</v>
+        <v>2942.394</v>
       </c>
       <c r="D11">
-        <v>1947.5450000000001</v>
+        <v>2772.886</v>
       </c>
       <c r="E11">
-        <v>2179.2170000000001</v>
+        <v>3115.446</v>
       </c>
       <c r="F11">
-        <v>3637.9140000000002</v>
+        <v>5216.507</v>
       </c>
       <c r="G11">
-        <v>3432.431</v>
+        <v>4905.449</v>
       </c>
       <c r="H11">
-        <v>3851.9679999999998</v>
+        <v>5537.445</v>
       </c>
       <c r="I11">
-        <v>155028017.31099999</v>
+        <v>221279871.736</v>
       </c>
       <c r="J11">
-        <v>146404317.48100001</v>
+        <v>208504949.596</v>
       </c>
       <c r="K11">
-        <v>163824978.991</v>
+        <v>234311993.746</v>
       </c>
       <c r="L11">
-        <v>483855512.778</v>
+        <v>693825457.704</v>
       </c>
       <c r="M11">
-        <v>456413429.30000001</v>
+        <v>652445074.47</v>
       </c>
       <c r="N11">
-        <v>512324804.10500002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
+        <v>736366505.0549999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C12">
-        <v>1589.586</v>
+        <v>2409.239</v>
       </c>
       <c r="D12">
-        <v>1509.83</v>
+        <v>2265.696</v>
       </c>
       <c r="E12">
-        <v>1670.5340000000001</v>
+        <v>2554.297</v>
       </c>
       <c r="F12">
-        <v>2817.1390000000001</v>
+        <v>4366.896</v>
       </c>
       <c r="G12">
-        <v>2673.5129999999999</v>
+        <v>4099.484</v>
       </c>
       <c r="H12">
-        <v>2963.2910000000002</v>
+        <v>4643.198</v>
       </c>
       <c r="I12">
-        <v>119551979.618</v>
+        <v>181173287.971</v>
       </c>
       <c r="J12">
-        <v>113582967.64</v>
+        <v>170473800.353</v>
       </c>
       <c r="K12">
-        <v>125621285.01800001</v>
+        <v>192187854.862</v>
       </c>
       <c r="L12">
-        <v>374643304.05699998</v>
+        <v>580768844.841</v>
       </c>
       <c r="M12">
-        <v>355596299.421</v>
+        <v>545160638.202</v>
       </c>
       <c r="N12">
-        <v>394125231.01599997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
+        <v>617299114.929</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C13">
-        <v>2502.239</v>
+        <v>4401.281</v>
       </c>
       <c r="D13">
-        <v>2385.7559999999999</v>
+        <v>4184.431</v>
       </c>
       <c r="E13">
-        <v>2620.712</v>
+        <v>4621.53</v>
       </c>
       <c r="F13">
-        <v>5079.8789999999999</v>
+        <v>9029.017</v>
       </c>
       <c r="G13">
-        <v>4835.1469999999999</v>
+        <v>8567.463</v>
       </c>
       <c r="H13">
-        <v>5328.3689999999997</v>
+        <v>9503.674000000001</v>
       </c>
       <c r="I13">
-        <v>188172838.92899999</v>
+        <v>331014953.614</v>
       </c>
       <c r="J13">
-        <v>179419234.86899999</v>
+        <v>314799737.976</v>
       </c>
       <c r="K13">
-        <v>197076931.24700001</v>
+        <v>347564497.689</v>
       </c>
       <c r="L13">
-        <v>675557738.55400002</v>
+        <v>1200787486.659</v>
       </c>
       <c r="M13">
-        <v>643040953.01199996</v>
+        <v>1139180263.4</v>
       </c>
       <c r="N13">
-        <v>708641003.199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
+        <v>1263827709.284</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C14">
-        <v>7213.7039999999997</v>
+        <v>8354.17</v>
       </c>
       <c r="D14">
-        <v>6674.7280000000001</v>
+        <v>7716.561</v>
       </c>
       <c r="E14">
-        <v>7755.7439999999997</v>
+        <v>8998.446</v>
       </c>
       <c r="F14">
-        <v>10776.984</v>
+        <v>12955.635</v>
       </c>
       <c r="G14">
-        <v>10110.023999999999</v>
+        <v>12111.836</v>
       </c>
       <c r="H14">
-        <v>11452.361999999999</v>
+        <v>13811.007</v>
       </c>
       <c r="I14">
-        <v>121477420.73</v>
+        <v>140693170.136</v>
       </c>
       <c r="J14">
-        <v>112414274.20299999</v>
+        <v>129996219.533</v>
       </c>
       <c r="K14">
-        <v>130611981.111</v>
+        <v>151534077.247</v>
       </c>
       <c r="L14">
-        <v>1433187243.799</v>
+        <v>1722819519.508</v>
       </c>
       <c r="M14">
-        <v>1344550931.6429999</v>
+        <v>1610248463.838</v>
       </c>
       <c r="N14">
-        <v>1522907246.3139999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
+        <v>1836779203.192</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C15">
-        <v>5565.41</v>
+        <v>6510.341</v>
       </c>
       <c r="D15">
-        <v>5172.7449999999999</v>
+        <v>6006.187</v>
       </c>
       <c r="E15">
-        <v>5963.2939999999999</v>
+        <v>7023.746</v>
       </c>
       <c r="F15">
-        <v>8304.1859999999997</v>
+        <v>10360.11</v>
       </c>
       <c r="G15">
-        <v>7874.326</v>
+        <v>9744.428</v>
       </c>
       <c r="H15">
-        <v>8737.8060000000005</v>
+        <v>10984.788</v>
       </c>
       <c r="I15">
-        <v>93710939.578999996</v>
+        <v>109611923.764</v>
       </c>
       <c r="J15">
-        <v>87085376.517000005</v>
+        <v>101107908.882</v>
       </c>
       <c r="K15">
-        <v>100379221.359</v>
+        <v>118225431.994</v>
       </c>
       <c r="L15">
-        <v>1104282255.8169999</v>
+        <v>1377714036.179</v>
       </c>
       <c r="M15">
-        <v>1047514511.451</v>
+        <v>1296088461.522</v>
       </c>
       <c r="N15">
-        <v>1162164992.642</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
+        <v>1461357977.197</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C16">
-        <v>6906.5789999999997</v>
+        <v>9256.993</v>
       </c>
       <c r="D16">
-        <v>6439.1279999999997</v>
+        <v>8593.724</v>
       </c>
       <c r="E16">
-        <v>7379.192</v>
+        <v>9926.467000000001</v>
       </c>
       <c r="F16">
-        <v>11261.063</v>
+        <v>15637.982</v>
       </c>
       <c r="G16">
-        <v>10637.398999999999</v>
+        <v>14726.846</v>
       </c>
       <c r="H16">
-        <v>11896.311</v>
+        <v>16566.756</v>
       </c>
       <c r="I16">
-        <v>116314411.59199999</v>
+        <v>155894440.922</v>
       </c>
       <c r="J16">
-        <v>108394180.913</v>
+        <v>144717717.16</v>
       </c>
       <c r="K16">
-        <v>124312662.065</v>
+        <v>167165893.565</v>
       </c>
       <c r="L16">
-        <v>1497944344.905</v>
+        <v>2080265419.713</v>
       </c>
       <c r="M16">
-        <v>1414513897.9449999</v>
+        <v>1958708067.075</v>
       </c>
       <c r="N16">
-        <v>1582087740.092</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
+        <v>2203165117.391</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C17">
-        <v>40472.983</v>
+        <v>60829.48</v>
       </c>
       <c r="D17">
-        <v>38821.135000000002</v>
+        <v>57592.823</v>
       </c>
       <c r="E17">
-        <v>42148.516000000003</v>
+        <v>64109.598</v>
       </c>
       <c r="F17">
-        <v>11432.064</v>
+        <v>17561.321</v>
       </c>
       <c r="G17">
-        <v>10792.565000000001</v>
+        <v>16188.766</v>
       </c>
       <c r="H17">
-        <v>12084.547</v>
+        <v>19003.63</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1202,39 +1185,43 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1520471945.813</v>
+        <v>2335879013.665</v>
       </c>
       <c r="M17">
-        <v>1435656257.882</v>
+        <v>2152736590.901</v>
       </c>
       <c r="N17">
-        <v>1607322757.135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
+        <v>2526434424.605</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C18">
-        <v>30091.127</v>
+        <v>47885.325</v>
       </c>
       <c r="D18">
-        <v>29029.477999999999</v>
+        <v>45511.246</v>
       </c>
       <c r="E18">
-        <v>31157.65</v>
+        <v>50247.679</v>
       </c>
       <c r="F18">
-        <v>8482.5310000000009</v>
+        <v>13920.005</v>
       </c>
       <c r="G18">
-        <v>8086.0079999999998</v>
+        <v>13006.974</v>
       </c>
       <c r="H18">
-        <v>8886.5519999999997</v>
+        <v>14850.111</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1246,39 +1233,43 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1128339741.9590001</v>
+        <v>1851655339.4</v>
       </c>
       <c r="M18">
-        <v>1075408459.9460001</v>
+        <v>1730690397.058</v>
       </c>
       <c r="N18">
-        <v>1182139869.437</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>17</v>
+        <v>1975411886.632</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C19">
-        <v>53804.46</v>
+        <v>100888.154</v>
       </c>
       <c r="D19">
-        <v>51975.673000000003</v>
+        <v>96595.337</v>
       </c>
       <c r="E19">
-        <v>55645.686999999998</v>
+        <v>105195.71</v>
       </c>
       <c r="F19">
-        <v>17973.893</v>
+        <v>34094.347</v>
       </c>
       <c r="G19">
-        <v>17143.719000000001</v>
+        <v>32173.224</v>
       </c>
       <c r="H19">
-        <v>18816.164000000001</v>
+        <v>36053.266</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1290,171 +1281,187 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2390829625.8060002</v>
+        <v>4535167093.505</v>
       </c>
       <c r="M19">
-        <v>2280890956.5019999</v>
+        <v>4281631303.208</v>
       </c>
       <c r="N19">
-        <v>2502589681.8579998</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
+        <v>4794812563.599</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C20">
-        <v>30606.289000000001</v>
+        <v>45008.172</v>
       </c>
       <c r="D20">
-        <v>29256.059000000001</v>
+        <v>42560.074</v>
       </c>
       <c r="E20">
-        <v>31977.754000000001</v>
+        <v>47515.035</v>
       </c>
       <c r="F20">
-        <v>42399.701999999997</v>
+        <v>65163.643</v>
       </c>
       <c r="G20">
-        <v>40221.582999999999</v>
+        <v>60862.572</v>
       </c>
       <c r="H20">
-        <v>44645.989000000001</v>
+        <v>69674.306</v>
       </c>
       <c r="I20">
-        <v>453150905.27100003</v>
+        <v>666389082.495</v>
       </c>
       <c r="J20">
-        <v>433242546.01800001</v>
+        <v>630204353.2309999</v>
       </c>
       <c r="K20">
-        <v>473491516.52600002</v>
+        <v>703623070.4530001</v>
       </c>
       <c r="L20">
-        <v>5638871931.2139997</v>
+        <v>8666270002.036999</v>
       </c>
       <c r="M20">
-        <v>5349579103.6900005</v>
+        <v>8095353740.826</v>
       </c>
       <c r="N20">
-        <v>5937409855.8260002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s">
-        <v>23</v>
+        <v>9266308145.786999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C21">
-        <v>54692.103999999992</v>
+        <v>70252.43700000001</v>
       </c>
       <c r="D21">
-        <v>51881.264999999999</v>
+        <v>66460.697</v>
       </c>
       <c r="E21">
-        <v>57538.472999999998</v>
+        <v>74081.288</v>
       </c>
       <c r="F21">
-        <v>46025.523999999998</v>
+        <v>61138.555</v>
       </c>
       <c r="G21">
-        <v>43920.148000000001</v>
+        <v>58130.747</v>
       </c>
       <c r="H21">
-        <v>48155.637999999999</v>
+        <v>64185.308</v>
       </c>
       <c r="I21">
-        <v>3046646640.5250001</v>
+        <v>3913574248.777</v>
       </c>
       <c r="J21">
-        <v>2889647616.2719998</v>
+        <v>3701361863.854</v>
       </c>
       <c r="K21">
-        <v>3205260331.4169998</v>
+        <v>4127473628.597</v>
       </c>
       <c r="L21">
-        <v>6121615644.4540005</v>
+        <v>8132050741.938</v>
       </c>
       <c r="M21">
-        <v>5841638947.1469994</v>
+        <v>7731299246.173</v>
       </c>
       <c r="N21">
-        <v>6405202659.7029991</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
+        <v>8535716942.035</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C22">
-        <v>19685.692999999999</v>
+        <v>24121.504</v>
       </c>
       <c r="D22">
-        <v>18286.600999999999</v>
+        <v>22316.472</v>
       </c>
       <c r="E22">
-        <v>21098.23</v>
+        <v>25948.659</v>
       </c>
       <c r="F22">
-        <v>30342.233</v>
+        <v>38953.727</v>
       </c>
       <c r="G22">
-        <v>28621.749</v>
+        <v>36583.11</v>
       </c>
       <c r="H22">
-        <v>32086.478999999999</v>
+        <v>41362.551</v>
       </c>
       <c r="I22">
-        <v>331502771.90100002</v>
+        <v>406199534.822</v>
       </c>
       <c r="J22">
-        <v>307893831.63300002</v>
+        <v>375821845.575</v>
       </c>
       <c r="K22">
-        <v>355303864.53500003</v>
+        <v>436925402.806</v>
       </c>
       <c r="L22">
-        <v>4035413844.5209999</v>
+        <v>5180798975.4</v>
       </c>
       <c r="M22">
-        <v>3806579341.039</v>
+        <v>4865044992.435</v>
       </c>
       <c r="N22">
-        <v>4267159979.0479999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
+        <v>5501302297.78</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C23">
-        <v>124368.57</v>
+        <v>209602.959</v>
       </c>
       <c r="D23">
-        <v>119826.28599999999</v>
+        <v>199699.406</v>
       </c>
       <c r="E23">
-        <v>128951.853</v>
+        <v>219552.987</v>
       </c>
       <c r="F23">
-        <v>37888.487999999998</v>
+        <v>65575.67300000001</v>
       </c>
       <c r="G23">
-        <v>36022.292000000001</v>
+        <v>61368.96399999999</v>
       </c>
       <c r="H23">
-        <v>39787.263000000014</v>
+        <v>69907.00700000001</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1466,83 +1473,91 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>5039641313.578001</v>
+        <v>8722701446.57</v>
       </c>
       <c r="M23">
-        <v>4791955674.3299999</v>
+        <v>8165058291.167</v>
       </c>
       <c r="N23">
-        <v>5292052308.4300003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>23</v>
+        <v>9296658874.835999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C24">
-        <v>6153.1399999999994</v>
+        <v>9752.914000000001</v>
       </c>
       <c r="D24">
-        <v>5843.1309999999994</v>
+        <v>9223.012999999999</v>
       </c>
       <c r="E24">
-        <v>6470.4629999999997</v>
+        <v>10291.273</v>
       </c>
       <c r="F24">
-        <v>11534.932000000001</v>
+        <v>18612.42</v>
       </c>
       <c r="G24">
-        <v>10941.091</v>
+        <v>17572.396</v>
       </c>
       <c r="H24">
-        <v>12143.628000000001</v>
+        <v>19684.317</v>
       </c>
       <c r="I24">
-        <v>462752835.85799998</v>
+        <v>733468113.3210001</v>
       </c>
       <c r="J24">
-        <v>439406519.99000001</v>
+        <v>693778487.925</v>
       </c>
       <c r="K24">
-        <v>486523195.25599998</v>
+        <v>774064346.2969999</v>
       </c>
       <c r="L24">
-        <v>1534056555.3889999</v>
+        <v>2475381789.204</v>
       </c>
       <c r="M24">
-        <v>1455050681.733</v>
+        <v>2336785976.072</v>
       </c>
       <c r="N24">
-        <v>1615091038.3199999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
+        <v>2617493329.268</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C25">
-        <v>99799.010999999999</v>
+        <v>110492.41</v>
       </c>
       <c r="D25">
-        <v>93299.828999999998</v>
+        <v>103334.398</v>
       </c>
       <c r="E25">
-        <v>106281.33199999999</v>
+        <v>117630.289</v>
       </c>
       <c r="F25">
-        <v>975153.57600000012</v>
+        <v>1111325.836</v>
       </c>
       <c r="G25">
-        <v>938203.08200000005</v>
+        <v>1068286.249</v>
       </c>
       <c r="H25">
-        <v>1012124.545</v>
+        <v>1154364.488</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1554,233 +1569,253 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>129701488512.02901</v>
+        <v>147811881791.09</v>
       </c>
       <c r="M25">
-        <v>124767884949.144</v>
+        <v>142075826019.593</v>
       </c>
       <c r="N25">
-        <v>134646867717.17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
+        <v>153573264702.61</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>periurban</t>
+        </is>
       </c>
       <c r="C26">
-        <v>113835.26700000001</v>
+        <v>146518.036</v>
       </c>
       <c r="D26">
-        <v>107518.17600000001</v>
+        <v>137722.21</v>
       </c>
       <c r="E26">
-        <v>120215.95299999999</v>
+        <v>155402.528</v>
       </c>
       <c r="F26">
-        <v>363653.71799999999</v>
+        <v>415048.237</v>
       </c>
       <c r="G26">
-        <v>347569.92200000002</v>
+        <v>395573.409</v>
       </c>
       <c r="H26">
-        <v>379826.65700000001</v>
+        <v>434734.932</v>
       </c>
       <c r="I26">
-        <v>1519689414.937</v>
+        <v>1887643349.277</v>
       </c>
       <c r="J26">
-        <v>1433437578.8640001</v>
+        <v>1776196954.119</v>
       </c>
       <c r="K26">
-        <v>1606815680.987</v>
+        <v>2000470939.401</v>
       </c>
       <c r="L26">
-        <v>48365229372.657013</v>
+        <v>55202190621.39001</v>
       </c>
       <c r="M26">
-        <v>46225485608.541</v>
+        <v>52607868017.627</v>
       </c>
       <c r="N26">
-        <v>50514419372.932007</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
+        <v>57822741289.241</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rural</t>
+        </is>
       </c>
       <c r="C27">
-        <v>91656.361999999994</v>
+        <v>120312.107</v>
       </c>
       <c r="D27">
-        <v>87078.963000000003</v>
+        <v>113518.659</v>
       </c>
       <c r="E27">
-        <v>96242.459000000003</v>
+        <v>127125.616</v>
       </c>
       <c r="F27">
-        <v>334301.13099999999</v>
+        <v>387464.569</v>
       </c>
       <c r="G27">
-        <v>321646.80300000001</v>
+        <v>371273.219</v>
       </c>
       <c r="H27">
-        <v>346983.58600000013</v>
+        <v>403733.6199999999</v>
       </c>
       <c r="I27">
-        <v>1200762968.421</v>
+        <v>1528166237.251</v>
       </c>
       <c r="J27">
-        <v>1140575522.608</v>
+        <v>1440686932.004</v>
       </c>
       <c r="K27">
-        <v>1261653441.6630001</v>
+        <v>1616924807.258</v>
       </c>
       <c r="L27">
-        <v>44460103001.008003</v>
+        <v>51528517833.04901</v>
       </c>
       <c r="M27">
-        <v>42773136236.831993</v>
+        <v>49375600890.777</v>
       </c>
       <c r="N27">
-        <v>46161825068.547997</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
+        <v>53710874474.489</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>urban</t>
+        </is>
       </c>
       <c r="C28">
-        <v>129813.178</v>
+        <v>202400.253</v>
       </c>
       <c r="D28">
-        <v>123796.03200000001</v>
+        <v>192353.191</v>
       </c>
       <c r="E28">
-        <v>135859.693</v>
+        <v>212491.387</v>
       </c>
       <c r="F28">
-        <v>445389.60600000003</v>
+        <v>558257.048</v>
       </c>
       <c r="G28">
-        <v>428713.22</v>
+        <v>535957.41</v>
       </c>
       <c r="H28">
-        <v>462133.29900000012</v>
+        <v>580709.425</v>
       </c>
       <c r="I28">
-        <v>1573600770.197</v>
+        <v>2303821392.887</v>
       </c>
       <c r="J28">
-        <v>1496177412.441</v>
+        <v>2184282664.462</v>
       </c>
       <c r="K28">
-        <v>1652109785.0840001</v>
+        <v>2424690701.494</v>
       </c>
       <c r="L28">
-        <v>59245755427.519997</v>
+        <v>74258376291.8</v>
       </c>
       <c r="M28">
-        <v>57014066851.709999</v>
+        <v>71285899357.862</v>
       </c>
       <c r="N28">
-        <v>61487539117.017014</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
+        <v>77257128528.586</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C29">
-        <v>335304.80699999997</v>
+        <v>469230.3959999999</v>
       </c>
       <c r="D29">
-        <v>318393.17099999997</v>
+        <v>443594.0599999999</v>
       </c>
       <c r="E29">
-        <v>352318.10499999998</v>
+        <v>495019.531</v>
       </c>
       <c r="F29">
-        <v>1143344.4550000001</v>
+        <v>1360769.854</v>
       </c>
       <c r="G29">
-        <v>1097929.9450000001</v>
+        <v>1302804.038</v>
       </c>
       <c r="H29">
-        <v>1188943.5419999999</v>
+        <v>1419177.977</v>
       </c>
       <c r="I29">
-        <v>4294053153.5549998</v>
+        <v>5719630979.415</v>
       </c>
       <c r="J29">
-        <v>4070190513.9130001</v>
+        <v>5401166550.584999</v>
       </c>
       <c r="K29">
-        <v>4520578907.7340002</v>
+        <v>6042086448.152999</v>
       </c>
       <c r="L29">
-        <v>152071087801.185</v>
+        <v>180989084746.239</v>
       </c>
       <c r="M29">
-        <v>146012688697.08301</v>
+        <v>173269368266.2661</v>
       </c>
       <c r="N29">
-        <v>158163783558.4971</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
+        <v>188790744292.316</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Morbidity</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C30">
-        <v>235505.796</v>
+        <v>358737.986</v>
       </c>
       <c r="D30">
-        <v>225093.342</v>
+        <v>340259.662</v>
       </c>
       <c r="E30">
-        <v>246036.77299999999</v>
+        <v>377389.242</v>
       </c>
       <c r="F30">
-        <v>168190.87899999999</v>
+        <v>249444.018</v>
       </c>
       <c r="G30">
-        <v>159726.86300000001</v>
+        <v>234517.789</v>
       </c>
       <c r="H30">
-        <v>176818.99699999989</v>
+        <v>264813.4890000001</v>
       </c>
       <c r="I30">
-        <v>4294053153.5549998</v>
+        <v>5719630979.415</v>
       </c>
       <c r="J30">
-        <v>4070190513.9130001</v>
+        <v>5401166550.584999</v>
       </c>
       <c r="K30">
-        <v>4520578907.7340002</v>
+        <v>6042086448.152999</v>
       </c>
       <c r="L30">
-        <v>22369599289.155998</v>
+        <v>33177202955.149</v>
       </c>
       <c r="M30">
-        <v>21244803747.938999</v>
+        <v>31193542246.673</v>
       </c>
       <c r="N30">
-        <v>23516915841.327</v>
+        <v>35217479589.706</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -1,21 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE412BBC-1A84-3C4B-8792-22D27389B718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="26360" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>area_type</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>periurban</t>
+  </si>
+  <si>
+    <t>rural</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +162,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +214,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +248,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +283,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,110 +459,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>area_type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>36806.308</v>
+        <v>36806.307999999997</v>
       </c>
       <c r="D2">
-        <v>34220.327</v>
+        <v>34220.326999999997</v>
       </c>
       <c r="E2">
-        <v>39394.16</v>
+        <v>39394.160000000003</v>
       </c>
       <c r="F2">
-        <v>341516.823</v>
+        <v>341516.82299999997</v>
       </c>
       <c r="G2">
         <v>326940.01</v>
       </c>
       <c r="H2">
-        <v>356098.202</v>
+        <v>356098.20199999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -465,43 +542,39 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45422491789.039</v>
+        <v>45422491789.039001</v>
       </c>
       <c r="M2">
         <v>43480886742.723</v>
       </c>
       <c r="N2">
-        <v>47365394777.025</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>47365394777.025002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
       </c>
       <c r="C3">
-        <v>33267.112</v>
+        <v>33267.112000000001</v>
       </c>
       <c r="D3">
-        <v>31175.505</v>
+        <v>31175.505000000001</v>
       </c>
       <c r="E3">
-        <v>35346.168</v>
+        <v>35346.167999999998</v>
       </c>
       <c r="F3">
-        <v>327423.941</v>
+        <v>327423.94099999999</v>
       </c>
       <c r="G3">
         <v>314910.033</v>
       </c>
       <c r="H3">
-        <v>339916.537</v>
+        <v>339916.53700000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -513,43 +586,39 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>43542526515.595</v>
+        <v>43542526515.595001</v>
       </c>
       <c r="M3">
-        <v>41879092249.947</v>
+        <v>41879092249.946999</v>
       </c>
       <c r="N3">
-        <v>45221777852.946</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>45221777852.945999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
       </c>
       <c r="C4">
         <v>40418.99</v>
       </c>
       <c r="D4">
-        <v>37938.566</v>
+        <v>37938.565999999999</v>
       </c>
       <c r="E4">
-        <v>42889.961</v>
+        <v>42889.961000000003</v>
       </c>
       <c r="F4">
-        <v>442385.072</v>
+        <v>442385.07199999999</v>
       </c>
       <c r="G4">
-        <v>426436.206</v>
+        <v>426436.20600000001</v>
       </c>
       <c r="H4">
-        <v>458349.749</v>
+        <v>458349.74900000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -561,49 +630,45 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>58846863486.456</v>
+        <v>58846863486.456001</v>
       </c>
       <c r="M4">
-        <v>56715847026.923</v>
+        <v>56715847026.922997</v>
       </c>
       <c r="N4">
         <v>60986092072.639</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>23697.925</v>
+        <v>23697.924999999999</v>
       </c>
       <c r="D5">
         <v>22335.302</v>
       </c>
       <c r="E5">
-        <v>25071.976</v>
+        <v>25071.975999999999</v>
       </c>
       <c r="F5">
-        <v>19319.041</v>
+        <v>19319.041000000001</v>
       </c>
       <c r="G5">
-        <v>18308.509</v>
+        <v>18308.508999999998</v>
       </c>
       <c r="H5">
-        <v>20338.657</v>
+        <v>20338.656999999999</v>
       </c>
       <c r="I5">
-        <v>1320056785.603</v>
+        <v>1320056785.6029999</v>
       </c>
       <c r="J5">
-        <v>1243989370.475</v>
+        <v>1243989370.4749999</v>
       </c>
       <c r="K5">
         <v>1396841057.494</v>
@@ -612,43 +677,39 @@
         <v>2569568285.112</v>
       </c>
       <c r="M5">
-        <v>2435084861.457</v>
+        <v>2435084861.4569998</v>
       </c>
       <c r="N5">
-        <v>2704838419.696</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>2704838419.6960001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>19304.705</v>
+        <v>19304.705000000002</v>
       </c>
       <c r="D6">
-        <v>18252.853</v>
+        <v>18252.852999999999</v>
       </c>
       <c r="E6">
-        <v>20371.584</v>
+        <v>20371.583999999999</v>
       </c>
       <c r="F6">
         <v>16592.355</v>
       </c>
       <c r="G6">
-        <v>15730.247</v>
+        <v>15730.246999999999</v>
       </c>
       <c r="H6">
         <v>17473.909</v>
       </c>
       <c r="I6">
-        <v>1075464482.121</v>
+        <v>1075464482.1210001</v>
       </c>
       <c r="J6">
         <v>1016486063.516</v>
@@ -657,73 +718,65 @@
         <v>1134949585.895</v>
       </c>
       <c r="L6">
-        <v>2207280545.385</v>
+        <v>2207280545.3850002</v>
       </c>
       <c r="M6">
-        <v>2091761912.935</v>
+        <v>2091761912.9349999</v>
       </c>
       <c r="N6">
-        <v>2323870695.911</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>2323870695.9109998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
       </c>
       <c r="C7">
-        <v>27249.807</v>
+        <v>27249.807000000001</v>
       </c>
       <c r="D7">
-        <v>25872.542</v>
+        <v>25872.542000000001</v>
       </c>
       <c r="E7">
-        <v>28637.728</v>
+        <v>28637.727999999999</v>
       </c>
       <c r="F7">
         <v>25227.159</v>
       </c>
       <c r="G7">
-        <v>24091.991</v>
+        <v>24091.991000000002</v>
       </c>
       <c r="H7">
-        <v>26372.742</v>
+        <v>26372.741999999998</v>
       </c>
       <c r="I7">
         <v>1518052981.053</v>
       </c>
       <c r="J7">
-        <v>1440886429.863</v>
+        <v>1440886429.8629999</v>
       </c>
       <c r="K7">
-        <v>1595682985.208</v>
+        <v>1595682985.2079999</v>
       </c>
       <c r="L7">
         <v>3355201911.441</v>
       </c>
       <c r="M7">
-        <v>3204452471.781</v>
+        <v>3204452471.7810001</v>
       </c>
       <c r="N7">
         <v>3507007826.428</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
       </c>
       <c r="C8">
         <v>13887.759</v>
@@ -741,13 +794,13 @@
         <v>17118.839</v>
       </c>
       <c r="H8">
-        <v>19945.991</v>
+        <v>19945.991000000002</v>
       </c>
       <c r="I8">
-        <v>205613521.802</v>
+        <v>205613521.80199999</v>
       </c>
       <c r="J8">
-        <v>193706414.515</v>
+        <v>193706414.51499999</v>
       </c>
       <c r="K8">
         <v>217783810.914</v>
@@ -756,22 +809,18 @@
         <v>2457606556.362</v>
       </c>
       <c r="M8">
-        <v>2276466284.238</v>
+        <v>2276466284.2379999</v>
       </c>
       <c r="N8">
-        <v>2652927959.668</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>2652927959.6680002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
       </c>
       <c r="C9">
         <v>10935.385</v>
@@ -783,298 +832,274 @@
         <v>11582.142</v>
       </c>
       <c r="F9">
-        <v>14801.262</v>
+        <v>14801.262000000001</v>
       </c>
       <c r="G9">
         <v>13782.053</v>
       </c>
       <c r="H9">
-        <v>15865.077</v>
+        <v>15865.076999999999</v>
       </c>
       <c r="I9">
-        <v>161916543.395</v>
+        <v>161916543.39500001</v>
       </c>
       <c r="J9">
-        <v>152619159.253</v>
+        <v>152619159.25299999</v>
       </c>
       <c r="K9">
         <v>171561934.507</v>
       </c>
       <c r="L9">
-        <v>1968572551.649</v>
+        <v>1968572551.6489999</v>
       </c>
       <c r="M9">
-        <v>1832807231.113</v>
+        <v>1832807231.1129999</v>
       </c>
       <c r="N9">
-        <v>2111156946.874</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>2111156946.8740001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>20185.028</v>
+        <v>20185.027999999998</v>
       </c>
       <c r="D10">
         <v>19168.591</v>
       </c>
       <c r="E10">
-        <v>21219.991</v>
+        <v>21219.991000000002</v>
       </c>
       <c r="F10">
-        <v>31883.471</v>
+        <v>31883.471000000001</v>
       </c>
       <c r="G10">
         <v>29961.68</v>
       </c>
       <c r="H10">
-        <v>33863.238</v>
+        <v>33863.237999999998</v>
       </c>
       <c r="I10">
-        <v>298859017.298</v>
+        <v>298859017.29799998</v>
       </c>
       <c r="J10">
         <v>283878779.463</v>
       </c>
       <c r="K10">
-        <v>314277325.032</v>
+        <v>314277325.03200001</v>
       </c>
       <c r="L10">
         <v>4240090894.026</v>
       </c>
       <c r="M10">
-        <v>3986080225.475</v>
+        <v>3986080225.4749999</v>
       </c>
       <c r="N10">
-        <v>4502223239.245</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>4502223239.2449999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>2942.394</v>
+        <v>2942.3939999999998</v>
       </c>
       <c r="D11">
         <v>2772.886</v>
       </c>
       <c r="E11">
-        <v>3115.446</v>
+        <v>3115.4459999999999</v>
       </c>
       <c r="F11">
-        <v>5216.507</v>
+        <v>5216.5069999999996</v>
       </c>
       <c r="G11">
-        <v>4905.449</v>
+        <v>4905.4489999999996</v>
       </c>
       <c r="H11">
-        <v>5537.445</v>
+        <v>5537.4449999999997</v>
       </c>
       <c r="I11">
         <v>221279871.736</v>
       </c>
       <c r="J11">
-        <v>208504949.596</v>
+        <v>208504949.59599999</v>
       </c>
       <c r="K11">
-        <v>234311993.746</v>
+        <v>234311993.74599999</v>
       </c>
       <c r="L11">
         <v>693825457.704</v>
       </c>
       <c r="M11">
-        <v>652445074.47</v>
+        <v>652445074.47000003</v>
       </c>
       <c r="N11">
-        <v>736366505.0549999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>736366505.05499995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
       </c>
       <c r="C12">
         <v>2409.239</v>
       </c>
       <c r="D12">
-        <v>2265.696</v>
+        <v>2265.6959999999999</v>
       </c>
       <c r="E12">
         <v>2554.297</v>
       </c>
       <c r="F12">
-        <v>4366.896</v>
+        <v>4366.8959999999997</v>
       </c>
       <c r="G12">
-        <v>4099.484</v>
+        <v>4099.4840000000004</v>
       </c>
       <c r="H12">
-        <v>4643.198</v>
+        <v>4643.1980000000003</v>
       </c>
       <c r="I12">
-        <v>181173287.971</v>
+        <v>181173287.97099999</v>
       </c>
       <c r="J12">
-        <v>170473800.353</v>
+        <v>170473800.35299999</v>
       </c>
       <c r="K12">
-        <v>192187854.862</v>
+        <v>192187854.86199999</v>
       </c>
       <c r="L12">
-        <v>580768844.841</v>
+        <v>580768844.84099996</v>
       </c>
       <c r="M12">
-        <v>545160638.202</v>
+        <v>545160638.20200002</v>
       </c>
       <c r="N12">
-        <v>617299114.929</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>617299114.92900002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>4401.281</v>
+        <v>4401.2809999999999</v>
       </c>
       <c r="D13">
-        <v>4184.431</v>
+        <v>4184.4309999999996</v>
       </c>
       <c r="E13">
         <v>4621.53</v>
       </c>
       <c r="F13">
-        <v>9029.017</v>
+        <v>9029.0169999999998</v>
       </c>
       <c r="G13">
-        <v>8567.463</v>
+        <v>8567.4629999999997</v>
       </c>
       <c r="H13">
-        <v>9503.674000000001</v>
+        <v>9503.6740000000009</v>
       </c>
       <c r="I13">
-        <v>331014953.614</v>
+        <v>331014953.61400002</v>
       </c>
       <c r="J13">
-        <v>314799737.976</v>
+        <v>314799737.97600001</v>
       </c>
       <c r="K13">
-        <v>347564497.689</v>
+        <v>347564497.68900001</v>
       </c>
       <c r="L13">
-        <v>1200787486.659</v>
+        <v>1200787486.6589999</v>
       </c>
       <c r="M13">
-        <v>1139180263.4</v>
+        <v>1139180263.4000001</v>
       </c>
       <c r="N13">
-        <v>1263827709.284</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>1263827709.2839999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
         <v>8354.17</v>
       </c>
       <c r="D14">
-        <v>7716.561</v>
+        <v>7716.5609999999997</v>
       </c>
       <c r="E14">
-        <v>8998.446</v>
+        <v>8998.4459999999999</v>
       </c>
       <c r="F14">
         <v>12955.635</v>
       </c>
       <c r="G14">
-        <v>12111.836</v>
+        <v>12111.835999999999</v>
       </c>
       <c r="H14">
         <v>13811.007</v>
       </c>
       <c r="I14">
-        <v>140693170.136</v>
+        <v>140693170.13600001</v>
       </c>
       <c r="J14">
-        <v>129996219.533</v>
+        <v>129996219.53300001</v>
       </c>
       <c r="K14">
-        <v>151534077.247</v>
+        <v>151534077.24700001</v>
       </c>
       <c r="L14">
-        <v>1722819519.508</v>
+        <v>1722819519.5079999</v>
       </c>
       <c r="M14">
-        <v>1610248463.838</v>
+        <v>1610248463.8380001</v>
       </c>
       <c r="N14">
-        <v>1836779203.192</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>1836779203.1919999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>6510.341</v>
+        <v>6510.3410000000003</v>
       </c>
       <c r="D15">
-        <v>6006.187</v>
+        <v>6006.1869999999999</v>
       </c>
       <c r="E15">
-        <v>7023.746</v>
+        <v>7023.7460000000001</v>
       </c>
       <c r="F15">
         <v>10360.11</v>
       </c>
       <c r="G15">
-        <v>9744.428</v>
+        <v>9744.4279999999999</v>
       </c>
       <c r="H15">
         <v>10984.788</v>
@@ -1089,34 +1114,30 @@
         <v>118225431.994</v>
       </c>
       <c r="L15">
-        <v>1377714036.179</v>
+        <v>1377714036.1789999</v>
       </c>
       <c r="M15">
-        <v>1296088461.522</v>
+        <v>1296088461.5220001</v>
       </c>
       <c r="N15">
         <v>1461357977.197</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>9256.993</v>
+        <v>9256.9930000000004</v>
       </c>
       <c r="D16">
-        <v>8593.724</v>
+        <v>8593.7240000000002</v>
       </c>
       <c r="E16">
-        <v>9926.467000000001</v>
+        <v>9926.4670000000006</v>
       </c>
       <c r="F16">
         <v>15637.982</v>
@@ -1125,10 +1146,10 @@
         <v>14726.846</v>
       </c>
       <c r="H16">
-        <v>16566.756</v>
+        <v>16566.756000000001</v>
       </c>
       <c r="I16">
-        <v>155894440.922</v>
+        <v>155894440.92199999</v>
       </c>
       <c r="J16">
         <v>144717717.16</v>
@@ -1137,34 +1158,30 @@
         <v>167165893.565</v>
       </c>
       <c r="L16">
-        <v>2080265419.713</v>
+        <v>2080265419.7130001</v>
       </c>
       <c r="M16">
         <v>1958708067.075</v>
       </c>
       <c r="N16">
-        <v>2203165117.391</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>2203165117.3909998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
       </c>
       <c r="C17">
         <v>60829.48</v>
       </c>
       <c r="D17">
-        <v>57592.823</v>
+        <v>57592.822999999997</v>
       </c>
       <c r="E17">
-        <v>64109.598</v>
+        <v>64109.597999999998</v>
       </c>
       <c r="F17">
         <v>17561.321</v>
@@ -1194,34 +1211,30 @@
         <v>2526434424.605</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
       </c>
       <c r="C18">
-        <v>47885.325</v>
+        <v>47885.324999999997</v>
       </c>
       <c r="D18">
-        <v>45511.246</v>
+        <v>45511.245999999999</v>
       </c>
       <c r="E18">
-        <v>50247.679</v>
+        <v>50247.678999999996</v>
       </c>
       <c r="F18">
-        <v>13920.005</v>
+        <v>13920.004999999999</v>
       </c>
       <c r="G18">
         <v>13006.974</v>
       </c>
       <c r="H18">
-        <v>14850.111</v>
+        <v>14850.111000000001</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1233,28 +1246,24 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1851655339.4</v>
+        <v>1851655339.4000001</v>
       </c>
       <c r="M18">
-        <v>1730690397.058</v>
+        <v>1730690397.0580001</v>
       </c>
       <c r="N18">
         <v>1975411886.632</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
       </c>
       <c r="C19">
-        <v>100888.154</v>
+        <v>100888.15399999999</v>
       </c>
       <c r="D19">
         <v>96595.337</v>
@@ -1263,13 +1272,13 @@
         <v>105195.71</v>
       </c>
       <c r="F19">
-        <v>34094.347</v>
+        <v>34094.347000000002</v>
       </c>
       <c r="G19">
-        <v>32173.224</v>
+        <v>32173.223999999998</v>
       </c>
       <c r="H19">
-        <v>36053.266</v>
+        <v>36053.266000000003</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1281,76 +1290,68 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>4535167093.505</v>
+        <v>4535167093.5050001</v>
       </c>
       <c r="M19">
-        <v>4281631303.208</v>
+        <v>4281631303.2080002</v>
       </c>
       <c r="N19">
         <v>4794812563.599</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>45008.172</v>
+        <v>45008.171999999999</v>
       </c>
       <c r="D20">
-        <v>42560.074</v>
+        <v>42560.074000000001</v>
       </c>
       <c r="E20">
-        <v>47515.035</v>
+        <v>47515.035000000003</v>
       </c>
       <c r="F20">
-        <v>65163.643</v>
+        <v>65163.642999999996</v>
       </c>
       <c r="G20">
         <v>60862.572</v>
       </c>
       <c r="H20">
-        <v>69674.306</v>
+        <v>69674.305999999997</v>
       </c>
       <c r="I20">
         <v>666389082.495</v>
       </c>
       <c r="J20">
-        <v>630204353.2309999</v>
+        <v>630204353.23099995</v>
       </c>
       <c r="K20">
-        <v>703623070.4530001</v>
+        <v>703623070.45300007</v>
       </c>
       <c r="L20">
-        <v>8666270002.036999</v>
+        <v>8666270002.0369987</v>
       </c>
       <c r="M20">
-        <v>8095353740.826</v>
+        <v>8095353740.8260002</v>
       </c>
       <c r="N20">
-        <v>9266308145.786999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>9266308145.7869987</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>70252.43700000001</v>
+        <v>70252.437000000005</v>
       </c>
       <c r="D21">
         <v>66460.697</v>
@@ -1362,106 +1363,98 @@
         <v>61138.555</v>
       </c>
       <c r="G21">
-        <v>58130.747</v>
+        <v>58130.747000000003</v>
       </c>
       <c r="H21">
-        <v>64185.308</v>
+        <v>64185.307999999997</v>
       </c>
       <c r="I21">
         <v>3913574248.777</v>
       </c>
       <c r="J21">
-        <v>3701361863.854</v>
+        <v>3701361863.8540001</v>
       </c>
       <c r="K21">
-        <v>4127473628.597</v>
+        <v>4127473628.5970001</v>
       </c>
       <c r="L21">
-        <v>8132050741.938</v>
+        <v>8132050741.9379997</v>
       </c>
       <c r="M21">
-        <v>7731299246.173</v>
+        <v>7731299246.1730003</v>
       </c>
       <c r="N21">
-        <v>8535716942.035</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>8535716942.0349998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>24121.504</v>
+        <v>24121.504000000001</v>
       </c>
       <c r="D22">
-        <v>22316.472</v>
+        <v>22316.472000000002</v>
       </c>
       <c r="E22">
         <v>25948.659</v>
       </c>
       <c r="F22">
-        <v>38953.727</v>
+        <v>38953.726999999999</v>
       </c>
       <c r="G22">
         <v>36583.11</v>
       </c>
       <c r="H22">
-        <v>41362.551</v>
+        <v>41362.550999999999</v>
       </c>
       <c r="I22">
-        <v>406199534.822</v>
+        <v>406199534.82200003</v>
       </c>
       <c r="J22">
-        <v>375821845.575</v>
+        <v>375821845.57499999</v>
       </c>
       <c r="K22">
-        <v>436925402.806</v>
+        <v>436925402.80599999</v>
       </c>
       <c r="L22">
-        <v>5180798975.4</v>
+        <v>5180798975.3999996</v>
       </c>
       <c r="M22">
-        <v>4865044992.435</v>
+        <v>4865044992.4350004</v>
       </c>
       <c r="N22">
-        <v>5501302297.78</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>5501302297.7799997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23">
         <v>209602.959</v>
       </c>
       <c r="D23">
-        <v>199699.406</v>
+        <v>199699.40599999999</v>
       </c>
       <c r="E23">
-        <v>219552.987</v>
+        <v>219552.98699999999</v>
       </c>
       <c r="F23">
         <v>65575.67300000001</v>
       </c>
       <c r="G23">
-        <v>61368.96399999999</v>
+        <v>61368.963999999993</v>
       </c>
       <c r="H23">
-        <v>69907.00700000001</v>
+        <v>69907.007000000012</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1473,52 +1466,48 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>8722701446.57</v>
+        <v>8722701446.5699997</v>
       </c>
       <c r="M23">
-        <v>8165058291.167</v>
+        <v>8165058291.1669998</v>
       </c>
       <c r="N23">
-        <v>9296658874.835999</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>9296658874.8359985</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>9752.914000000001</v>
+        <v>9752.9140000000007</v>
       </c>
       <c r="D24">
         <v>9223.012999999999</v>
       </c>
       <c r="E24">
-        <v>10291.273</v>
+        <v>10291.272999999999</v>
       </c>
       <c r="F24">
-        <v>18612.42</v>
+        <v>18612.419999999998</v>
       </c>
       <c r="G24">
-        <v>17572.396</v>
+        <v>17572.396000000001</v>
       </c>
       <c r="H24">
-        <v>19684.317</v>
+        <v>19684.316999999999</v>
       </c>
       <c r="I24">
         <v>733468113.3210001</v>
       </c>
       <c r="J24">
-        <v>693778487.925</v>
+        <v>693778487.92499995</v>
       </c>
       <c r="K24">
-        <v>774064346.2969999</v>
+        <v>774064346.29699993</v>
       </c>
       <c r="L24">
         <v>2475381789.204</v>
@@ -1527,19 +1516,15 @@
         <v>2336785976.072</v>
       </c>
       <c r="N24">
-        <v>2617493329.268</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>2617493329.2680001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
       </c>
       <c r="C25">
         <v>110492.41</v>
@@ -1551,13 +1536,13 @@
         <v>117630.289</v>
       </c>
       <c r="F25">
-        <v>1111325.836</v>
+        <v>1111325.8359999999</v>
       </c>
       <c r="G25">
-        <v>1068286.249</v>
+        <v>1068286.2490000001</v>
       </c>
       <c r="H25">
-        <v>1154364.488</v>
+        <v>1154364.4879999999</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1572,40 +1557,36 @@
         <v>147811881791.09</v>
       </c>
       <c r="M25">
-        <v>142075826019.593</v>
+        <v>142075826019.59299</v>
       </c>
       <c r="N25">
-        <v>153573264702.61</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>periurban</t>
-        </is>
+        <v>153573264702.60999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>146518.036</v>
+        <v>146518.03599999999</v>
       </c>
       <c r="D26">
         <v>137722.21</v>
       </c>
       <c r="E26">
-        <v>155402.528</v>
+        <v>155402.52799999999</v>
       </c>
       <c r="F26">
-        <v>415048.237</v>
+        <v>415048.23700000002</v>
       </c>
       <c r="G26">
-        <v>395573.409</v>
+        <v>395573.40899999999</v>
       </c>
       <c r="H26">
-        <v>434734.932</v>
+        <v>434734.93199999997</v>
       </c>
       <c r="I26">
         <v>1887643349.277</v>
@@ -1617,25 +1598,21 @@
         <v>2000470939.401</v>
       </c>
       <c r="L26">
-        <v>55202190621.39001</v>
+        <v>55202190621.390007</v>
       </c>
       <c r="M26">
-        <v>52607868017.627</v>
+        <v>52607868017.626999</v>
       </c>
       <c r="N26">
-        <v>57822741289.241</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
+        <v>57822741289.240997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
       </c>
       <c r="C27">
         <v>120312.107</v>
@@ -1644,109 +1621,101 @@
         <v>113518.659</v>
       </c>
       <c r="E27">
-        <v>127125.616</v>
+        <v>127125.61599999999</v>
       </c>
       <c r="F27">
-        <v>387464.569</v>
+        <v>387464.56900000002</v>
       </c>
       <c r="G27">
-        <v>371273.219</v>
+        <v>371273.21899999998</v>
       </c>
       <c r="H27">
-        <v>403733.6199999999</v>
+        <v>403733.61999999988</v>
       </c>
       <c r="I27">
-        <v>1528166237.251</v>
+        <v>1528166237.2509999</v>
       </c>
       <c r="J27">
-        <v>1440686932.004</v>
+        <v>1440686932.0039999</v>
       </c>
       <c r="K27">
-        <v>1616924807.258</v>
+        <v>1616924807.2579999</v>
       </c>
       <c r="L27">
-        <v>51528517833.04901</v>
+        <v>51528517833.049011</v>
       </c>
       <c r="M27">
         <v>49375600890.777</v>
       </c>
       <c r="N27">
-        <v>53710874474.489</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
+        <v>53710874474.488998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
       </c>
       <c r="C28">
         <v>202400.253</v>
       </c>
       <c r="D28">
-        <v>192353.191</v>
+        <v>192353.19099999999</v>
       </c>
       <c r="E28">
-        <v>212491.387</v>
+        <v>212491.38699999999</v>
       </c>
       <c r="F28">
-        <v>558257.048</v>
+        <v>558257.04799999995</v>
       </c>
       <c r="G28">
         <v>535957.41</v>
       </c>
       <c r="H28">
-        <v>580709.425</v>
+        <v>580709.42500000005</v>
       </c>
       <c r="I28">
-        <v>2303821392.887</v>
+        <v>2303821392.8870001</v>
       </c>
       <c r="J28">
-        <v>2184282664.462</v>
+        <v>2184282664.4619999</v>
       </c>
       <c r="K28">
         <v>2424690701.494</v>
       </c>
       <c r="L28">
-        <v>74258376291.8</v>
+        <v>74258376291.800003</v>
       </c>
       <c r="M28">
         <v>71285899357.862</v>
       </c>
       <c r="N28">
-        <v>77257128528.586</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>77257128528.585999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>469230.3959999999</v>
+        <v>469230.39599999989</v>
       </c>
       <c r="D29">
-        <v>443594.0599999999</v>
+        <v>443594.05999999988</v>
       </c>
       <c r="E29">
-        <v>495019.531</v>
+        <v>495019.53100000002</v>
       </c>
       <c r="F29">
-        <v>1360769.854</v>
+        <v>1360769.8540000001</v>
       </c>
       <c r="G29">
-        <v>1302804.038</v>
+        <v>1302804.0379999999</v>
       </c>
       <c r="H29">
         <v>1419177.977</v>
@@ -1755,67 +1724,63 @@
         <v>5719630979.415</v>
       </c>
       <c r="J29">
-        <v>5401166550.584999</v>
+        <v>5401166550.5849991</v>
       </c>
       <c r="K29">
-        <v>6042086448.152999</v>
+        <v>6042086448.1529989</v>
       </c>
       <c r="L29">
-        <v>180989084746.239</v>
+        <v>180989084746.23901</v>
       </c>
       <c r="M29">
-        <v>173269368266.2661</v>
+        <v>173269368266.26611</v>
       </c>
       <c r="N29">
-        <v>188790744292.316</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+        <v>188790744292.31601</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
       </c>
       <c r="C30">
-        <v>358737.986</v>
+        <v>358737.98599999998</v>
       </c>
       <c r="D30">
-        <v>340259.662</v>
+        <v>340259.66200000001</v>
       </c>
       <c r="E30">
-        <v>377389.242</v>
+        <v>377389.24200000003</v>
       </c>
       <c r="F30">
-        <v>249444.018</v>
+        <v>249444.01800000001</v>
       </c>
       <c r="G30">
-        <v>234517.789</v>
+        <v>234517.78899999999</v>
       </c>
       <c r="H30">
-        <v>264813.4890000001</v>
+        <v>264813.48900000012</v>
       </c>
       <c r="I30">
         <v>5719630979.415</v>
       </c>
       <c r="J30">
-        <v>5401166550.584999</v>
+        <v>5401166550.5849991</v>
       </c>
       <c r="K30">
-        <v>6042086448.152999</v>
+        <v>6042086448.1529989</v>
       </c>
       <c r="L30">
-        <v>33177202955.149</v>
+        <v>33177202955.148998</v>
       </c>
       <c r="M30">
         <v>31193542246.673</v>
       </c>
       <c r="N30">
-        <v>35217479589.706</v>
+        <v>35217479589.706001</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
+++ b/output/Tables/Best practice/HIA_best_practice_1000replicate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Best practice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE412BBC-1A84-3C4B-8792-22D27389B718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCAFBC4C-B2C9-7E4B-BEEA-F2BE981EE48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="26360" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -462,6 +462,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="9.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
